--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="50" customWidth="1" style="32" min="1" max="1"/>
@@ -668,6 +668,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="33">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -926,6 +927,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="36" t="inlineStr">
         <is>
@@ -1217,6 +1219,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="33">
       <c r="A23" s="36" t="inlineStr">
         <is>
@@ -1438,6 +1441,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="33">
       <c r="A31" s="36" t="inlineStr">
         <is>
@@ -1497,7 +1501,7 @@
     <row r="33" ht="15" customHeight="1" s="33">
       <c r="A33" s="40" t="inlineStr">
         <is>
-          <t>Estes 24 in rip-stop nylon parachute</t>
+          <t>Estes 18 in rip-stop nylon parachute (FLIGHT canopy - CHUTE_D=0.4572 m in all sims)</t>
         </is>
       </c>
       <c r="B33" s="41" t="inlineStr">
@@ -1515,12 +1519,16 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="E33" s="43" t="n"/>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>CORRECTED 2026-08: line said 24 in. Every sim uses 18 in (6.2 m/s descent).</t>
+        </is>
+      </c>
       <c r="F33" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="45" t="n">
-        <v>10.25</v>
+        <v>9.99</v>
       </c>
       <c r="H33" s="45">
         <f>F33*G33</f>
@@ -1647,6 +1655,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="15" customHeight="1" s="33">
       <c r="A39" s="36" t="inlineStr">
         <is>
@@ -1934,6 +1943,7 @@
         <v/>
       </c>
     </row>
+    <row r="48"/>
     <row r="49" ht="15" customHeight="1" s="33">
       <c r="A49" s="36" t="inlineStr">
         <is>
@@ -2192,6 +2202,7 @@
         <v/>
       </c>
     </row>
+    <row r="57"/>
     <row r="58" ht="15" customHeight="1" s="33">
       <c r="A58" s="36" t="inlineStr">
         <is>
@@ -2730,277 +2741,292 @@
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="33">
-      <c r="A73" s="46" t="inlineStr">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>microSD SPI breakout board (SPI0 GP2-5; Pico has no SD slot)</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>PID 254</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>MISSING FROM BOM until 2026-08 - firmware sd_logger.h requires it</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H73" s="32">
+        <f>F73*G73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>1010 launch rail + pad (rail-exit gate is 1.0 m of rail)</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>Estes/Amazon</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>1010 rail</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>MISSING FROM BOM until 2026-08 - controller was costed, rail was not</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="H74" s="32">
+        <f>F74*G74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="33">
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>Nomex chute protector blanket (ejection-gas shield)</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>12x12 in Nomex</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>MISSING FROM BOM until 2026-08 - wadding is not equivalent for a bypass gas path</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H75" s="32">
+        <f>F75*G75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="33">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>Handheld anemometer (launch-site wind; RQ3 margin + go/no-go)</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>vane anemometer</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>MISSING FROM BOM until 2026-08 - we4_flight_reduce.py --wind needs a measurement</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H76" s="32">
+        <f>F76*G76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="33">
+      <c r="A77" s="32" t="inlineStr">
+        <is>
+          <t>Steel blast deflector plate (static stand; PC-FR will not survive)</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>mild steel ~150 mm sq</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>MISSING FROM BOM until 2026-08 - CAD generates a printable one, plume needs steel</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="H77" s="32">
+        <f>F77*G77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="33">
+      <c r="A78" s="46" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B73" s="47" t="n"/>
-      <c r="C73" s="47" t="n"/>
-      <c r="D73" s="47" t="n"/>
-      <c r="E73" s="47" t="n"/>
-      <c r="F73" s="47" t="n"/>
-      <c r="G73" s="47" t="n"/>
-      <c r="H73" s="48">
-        <f>SUM(H60:H72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="33">
-      <c r="A75" s="36" t="inlineStr">
+      <c r="B78" s="47" t="n"/>
+      <c r="C78" s="47" t="n"/>
+      <c r="D78" s="47" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/4543</t>
+        </is>
+      </c>
+      <c r="E78" s="47" t="n"/>
+      <c r="F78" s="47" t="n"/>
+      <c r="G78" s="47" t="n"/>
+      <c r="H78" s="48">
+        <f>SUM(H60:H77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="33">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/5974</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="33">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>8. Ground test - TVC balance + static stand (load cells + DAQ)</t>
         </is>
       </c>
-      <c r="B75" s="37" t="n"/>
-      <c r="C75" s="37" t="n"/>
-      <c r="D75" s="37" t="n"/>
-      <c r="E75" s="37" t="n"/>
-      <c r="F75" s="37" t="n"/>
-      <c r="G75" s="37" t="n"/>
-      <c r="H75" s="37" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="33">
-      <c r="A76" s="38" t="inlineStr">
+      <c r="B80" s="37" t="n"/>
+      <c r="C80" s="37" t="n"/>
+      <c r="D80" s="37" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/5302</t>
+        </is>
+      </c>
+      <c r="E80" s="37" t="n"/>
+      <c r="F80" s="37" t="n"/>
+      <c r="G80" s="37" t="n"/>
+      <c r="H80" s="37" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="33">
+      <c r="A81" s="38" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B76" s="38" t="inlineStr">
+      <c r="B81" s="38" t="inlineStr">
         <is>
           <t>Storefront</t>
         </is>
       </c>
-      <c r="C76" s="38" t="inlineStr">
+      <c r="C81" s="38" t="inlineStr">
         <is>
           <t>Part # / Spec</t>
         </is>
       </c>
-      <c r="D76" s="38" t="inlineStr">
+      <c r="D81" s="38" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="E76" s="38" t="inlineStr">
+      <c r="E81" s="38" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F76" s="39" t="inlineStr">
+      <c r="F81" s="39" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G76" s="39" t="inlineStr">
+      <c r="G81" s="39" t="inlineStr">
         <is>
           <t>Unit ($)</t>
         </is>
       </c>
-      <c r="H76" s="39" t="inlineStr">
+      <c r="H81" s="39" t="inlineStr">
         <is>
           <t>Line ($)</t>
         </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="33">
-      <c r="A77" s="40" t="inlineStr">
-        <is>
-          <t>Adafruit strain-gauge load cell 1 kg (lateral X,Y)</t>
-        </is>
-      </c>
-      <c r="B77" s="41" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>PID 4540</t>
-        </is>
-      </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E77" s="43" t="inlineStr">
-        <is>
-          <t>in Adafruit cart</t>
-        </is>
-      </c>
-      <c r="F77" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" s="45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H77" s="45">
-        <f>F77*G77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="33">
-      <c r="A78" s="40" t="inlineStr">
-        <is>
-          <t>Adafruit strain-gauge load cell 20 kg (static stand)</t>
-        </is>
-      </c>
-      <c r="B78" s="41" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>PID 4543</t>
-        </is>
-      </c>
-      <c r="D78" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E78" s="43" t="inlineStr">
-        <is>
-          <t>in Adafruit cart</t>
-        </is>
-      </c>
-      <c r="F78" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G78" s="45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H78" s="45">
-        <f>F78*G78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="33">
-      <c r="A79" s="40" t="inlineStr">
-        <is>
-          <t>Adafruit HX711 24-bit ADC</t>
-        </is>
-      </c>
-      <c r="B79" s="41" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>PID 5974</t>
-        </is>
-      </c>
-      <c r="D79" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E79" s="43" t="inlineStr">
-        <is>
-          <t>in Adafruit cart</t>
-        </is>
-      </c>
-      <c r="F79" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="45" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="H79" s="45">
-        <f>F79*G79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="33">
-      <c r="A80" s="40" t="inlineStr">
-        <is>
-          <t>Adafruit KB2040 (RP2040) - spare/bench DAQ</t>
-        </is>
-      </c>
-      <c r="B80" s="41" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>PID 5302</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E80" s="43" t="inlineStr">
-        <is>
-          <t>FREE w/ order</t>
-        </is>
-      </c>
-      <c r="F80" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="45">
-        <f>F80*G80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="33">
-      <c r="A81" s="40" t="inlineStr">
-        <is>
-          <t>Digital load cell + HX711, 5 kg (2 sets) - axial Z</t>
-        </is>
-      </c>
-      <c r="B81" s="41" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>B09K7G3477</t>
-        </is>
-      </c>
-      <c r="D81" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E81" s="43" t="inlineStr">
-        <is>
-          <t>in cart</t>
-        </is>
-      </c>
-      <c r="F81" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="45" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H81" s="45">
-        <f>F81*G81</f>
-        <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="33">
       <c r="A82" s="40" t="inlineStr">
         <is>
-          <t>UCEC calibration weight set 10 mg-100 g</t>
+          <t>Adafruit strain-gauge load cell 1 kg (lateral X,Y)</t>
         </is>
       </c>
       <c r="B82" s="41" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C82" s="41" t="inlineStr">
         <is>
-          <t>B08R8RGCRS</t>
+          <t>PID 4540</t>
         </is>
       </c>
       <c r="D82" s="42" t="inlineStr">
@@ -3010,14 +3036,14 @@
       </c>
       <c r="E82" s="43" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>in Adafruit cart</t>
         </is>
       </c>
       <c r="F82" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" s="45" t="n">
-        <v>9.99</v>
+        <v>3.95</v>
       </c>
       <c r="H82" s="45">
         <f>F82*G82</f>
@@ -3025,73 +3051,253 @@
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="33">
-      <c r="A83" s="46" t="inlineStr">
+      <c r="A83" s="40" t="inlineStr">
+        <is>
+          <t>Adafruit strain-gauge load cell 20 kg (static stand)</t>
+        </is>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>PID 4543</t>
+        </is>
+      </c>
+      <c r="D83" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E83" s="43" t="inlineStr">
+        <is>
+          <t>in Adafruit cart</t>
+        </is>
+      </c>
+      <c r="F83" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="45" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H83" s="45">
+        <f>F83*G83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="40" t="inlineStr">
+        <is>
+          <t>Adafruit HX711 24-bit ADC</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>PID 5974</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E84" s="43" t="inlineStr">
+        <is>
+          <t>in Adafruit cart</t>
+        </is>
+      </c>
+      <c r="F84" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="45" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="H84" s="45">
+        <f>F84*G84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="33">
+      <c r="A85" s="40" t="inlineStr">
+        <is>
+          <t>Adafruit KB2040 (RP2040) - spare/bench DAQ</t>
+        </is>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>PID 5302</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E85" s="43" t="inlineStr">
+        <is>
+          <t>FREE w/ order</t>
+        </is>
+      </c>
+      <c r="F85" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="45">
+        <f>F85*G85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="33">
+      <c r="A86" s="40" t="inlineStr">
+        <is>
+          <t>Digital load cell + HX711, 5 kg (2 sets) - axial Z</t>
+        </is>
+      </c>
+      <c r="B86" s="41" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>B09K7G3477</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E86" s="43" t="inlineStr">
+        <is>
+          <t>in cart</t>
+        </is>
+      </c>
+      <c r="F86" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="45" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H86" s="45">
+        <f>F86*G86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="33">
+      <c r="A87" s="40" t="inlineStr">
+        <is>
+          <t>UCEC calibration weight set 10 mg-100 g</t>
+        </is>
+      </c>
+      <c r="B87" s="41" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>B08R8RGCRS</t>
+        </is>
+      </c>
+      <c r="D87" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E87" s="43" t="inlineStr">
+        <is>
+          <t>in cart</t>
+        </is>
+      </c>
+      <c r="F87" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="45" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H87" s="45">
+        <f>F87*G87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="33">
+      <c r="A88" s="46" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B83" s="47" t="n"/>
-      <c r="C83" s="47" t="n"/>
-      <c r="D83" s="47" t="n"/>
-      <c r="E83" s="47" t="n"/>
-      <c r="F83" s="47" t="n"/>
-      <c r="G83" s="47" t="n"/>
-      <c r="H83" s="48">
-        <f>SUM(H77:H82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85" ht="15" customHeight="1" s="33">
-      <c r="A85" s="49" t="inlineStr">
+      <c r="B88" s="47" t="n"/>
+      <c r="C88" s="47" t="n"/>
+      <c r="D88" s="47" t="n"/>
+      <c r="E88" s="47" t="n"/>
+      <c r="F88" s="47" t="n"/>
+      <c r="G88" s="47" t="n"/>
+      <c r="H88" s="48">
+        <f>SUM(H82:H87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="33"/>
+    <row r="90" ht="15" customHeight="1" s="33">
+      <c r="A90" s="49" t="inlineStr">
         <is>
           <t>GROSS TO-BUY TOTAL</t>
         </is>
       </c>
-      <c r="B85" s="50" t="n"/>
-      <c r="C85" s="50" t="n"/>
-      <c r="D85" s="50" t="n"/>
-      <c r="E85" s="50" t="n"/>
-      <c r="F85" s="50" t="n"/>
-      <c r="G85" s="50" t="n"/>
-      <c r="H85" s="51">
-        <f>H11+H21+H29+H37+H47+H56+H73+H83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="33">
-      <c r="A86" s="52" t="inlineStr">
+      <c r="B90" s="50" t="n"/>
+      <c r="C90" s="50" t="n"/>
+      <c r="D90" s="50" t="n"/>
+      <c r="E90" s="50" t="n"/>
+      <c r="F90" s="50" t="n"/>
+      <c r="G90" s="50" t="n"/>
+      <c r="H90" s="51">
+        <f>H11+H21+H29+H37+H47+H56+H78+H88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="33">
+      <c r="A91" s="52" t="inlineStr">
         <is>
           <t>Less: Estes Pro Series II Launch Controller (reimbursed)</t>
         </is>
       </c>
-      <c r="H86" s="53">
+      <c r="H91" s="53">
         <f>-43.99</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="33">
-      <c r="A87" s="54" t="inlineStr">
+    <row r="92" ht="15" customHeight="1" s="33">
+      <c r="A92" s="54" t="inlineStr">
         <is>
           <t>NET OUT-OF-POCKET (still to buy)</t>
         </is>
       </c>
-      <c r="B87" s="50" t="n"/>
-      <c r="C87" s="50" t="n"/>
-      <c r="D87" s="50" t="n"/>
-      <c r="E87" s="50" t="n"/>
-      <c r="F87" s="50" t="n"/>
-      <c r="G87" s="50" t="n"/>
-      <c r="H87" s="55">
-        <f>H85+H86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="33"/>
-    <row r="89" ht="15" customHeight="1" s="33"/>
-    <row r="90" ht="15" customHeight="1" s="33"/>
-    <row r="91" ht="15" customHeight="1" s="33"/>
-    <row r="92" ht="15" customHeight="1" s="33"/>
+      <c r="B92" s="50" t="n"/>
+      <c r="C92" s="50" t="n"/>
+      <c r="D92" s="50" t="n"/>
+      <c r="E92" s="50" t="n"/>
+      <c r="F92" s="50" t="n"/>
+      <c r="G92" s="50" t="n"/>
+      <c r="H92" s="55">
+        <f>H90+H91</f>
+        <v/>
+      </c>
+    </row>
     <row r="93" ht="15" customHeight="1" s="33"/>
     <row r="94" ht="15" customHeight="1" s="33"/>
     <row r="95" ht="15" customHeight="1" s="33"/>
@@ -4184,7 +4390,7 @@
         </is>
       </c>
       <c r="B9" s="60">
-        <f>BOM!H73</f>
+        <f>BOM!H78</f>
         <v/>
       </c>
     </row>
@@ -4195,7 +4401,7 @@
         </is>
       </c>
       <c r="B10" s="60">
-        <f>BOM!H83</f>
+        <f>BOM!H88</f>
         <v/>
       </c>
     </row>
@@ -4207,7 +4413,7 @@
         </is>
       </c>
       <c r="B12" s="62">
-        <f>BOM!H85</f>
+        <f>BOM!H90</f>
         <v/>
       </c>
     </row>
@@ -4229,7 +4435,7 @@
         </is>
       </c>
       <c r="B14" s="64">
-        <f>BOM!H87</f>
+        <f>BOM!H92</f>
         <v/>
       </c>
     </row>

--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="50" customWidth="1" style="32" min="1" max="1"/>
@@ -1501,7 +1501,7 @@
     <row r="33" ht="15" customHeight="1" s="33">
       <c r="A33" s="40" t="inlineStr">
         <is>
-          <t>Estes 18 in rip-stop nylon parachute (FLIGHT canopy - CHUTE_D=0.4572 m in all sims)</t>
+          <t>Estes 24 in rip-stop nylon parachute (FLIGHT canopy - CHUTE_D=0.6096 m in all sims)</t>
         </is>
       </c>
       <c r="B33" s="41" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="E33" s="43" t="inlineStr">
         <is>
-          <t>CORRECTED 2026-08: line said 24 in. Every sim uses 18 in (6.2 m/s descent).</t>
+          <t>2026-08b: switched 18 in -&gt; 24 in. Descent 6.7 -&gt; 5.0 m/s.</t>
         </is>
       </c>
       <c r="F33" s="44" t="n">
         <v>4</v>
       </c>
       <c r="G33" s="45" t="n">
-        <v>9.99</v>
+        <v>10.25</v>
       </c>
       <c r="H33" s="45">
         <f>F33*G33</f>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="E42" s="43" t="inlineStr">
         <is>
-          <t>10 motors</t>
+          <t>Static thrust curves + MTVC + servo TVC on the balance (jetvane dropped).</t>
         </is>
       </c>
       <c r="F42" s="44" t="n">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E43" s="43" t="inlineStr">
         <is>
-          <t>6 motors; price est.</t>
+          <t>Stand commissioning, 2 firings per stand (Gate 5). NOT in the current cart.</t>
         </is>
       </c>
       <c r="F43" s="44" t="n">
@@ -1844,7 +1844,11 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="E44" s="43" t="n"/>
+      <c r="E44" s="43" t="inlineStr">
+        <is>
+          <t>Static thrust curves + MTVC + servo TVC on the balance (jetvane dropped).</t>
+        </is>
+      </c>
       <c r="F44" s="44" t="n">
         <v>1</v>
       </c>
@@ -1877,9 +1881,13 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="E45" s="43" t="n"/>
+      <c r="E45" s="43" t="inlineStr">
+        <is>
+          <t>6 per pack; ~15 firings planned. Cart has 1 pack - short.</t>
+        </is>
+      </c>
       <c r="F45" s="44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45" s="45" t="n">
         <v>6.99</v>
@@ -1947,7 +1955,7 @@
     <row r="49" ht="15" customHeight="1" s="33">
       <c r="A49" s="36" t="inlineStr">
         <is>
-          <t>6. Airframe filament (Amazon + Bambu ASA-Aero)</t>
+          <t>6. Airframe filament (PLA primary + PETG-CF owned)</t>
         </is>
       </c>
       <c r="B49" s="37" t="n"/>
@@ -2023,14 +2031,14 @@
       </c>
       <c r="E51" s="43" t="inlineStr">
         <is>
-          <t>in cart; bulkheads/engine/gimbal</t>
+          <t>REMOVED 2026-08b: PC-FR is out of the design (PLA/PETG-CF now). PETG-CF is already owned.</t>
         </is>
       </c>
       <c r="F51" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="45" t="n">
-        <v>49.99</v>
+        <v>0</v>
       </c>
       <c r="H51" s="45">
         <f>F51*G51</f>
@@ -2060,14 +2068,14 @@
       </c>
       <c r="E52" s="43" t="inlineStr">
         <is>
-          <t>$93.67 / 2 kg; Bambu-only</t>
+          <t>REMOVED 2026-08b: ASA-Aero is out of the design. Primary structure is now PLA.</t>
         </is>
       </c>
       <c r="F52" s="44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="45" t="n">
-        <v>46.835</v>
+        <v>0</v>
       </c>
       <c r="H52" s="45">
         <f>F52*G52</f>
@@ -2097,14 +2105,14 @@
       </c>
       <c r="E53" s="43" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>REMOVED 2026-08b: ABS was jetvane coupon material only; jetvane testing dropped.</t>
         </is>
       </c>
       <c r="F53" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="45" t="n">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="H53" s="45">
         <f>F53*G53</f>
@@ -2134,14 +2142,14 @@
       </c>
       <c r="E54" s="43" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>REMOVED 2026-08b: pure-PC coupons belonged to the retired zoned-materials RQ2.</t>
         </is>
       </c>
       <c r="F54" s="44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="45" t="n">
-        <v>30.39</v>
+        <v>0</v>
       </c>
       <c r="H54" s="45">
         <f>F54*G54</f>
@@ -2151,7 +2159,7 @@
     <row r="55" ht="15" customHeight="1" s="33">
       <c r="A55" s="40" t="inlineStr">
         <is>
-          <t>ELEGOO PLA+, Black - 4 kg (fins + wind tunnel)</t>
+          <t>Bambu/generic PLA 1.75 mm - PRIMARY AIRFRAME (nose, bay tubes, fins) - 1 kg</t>
         </is>
       </c>
       <c r="B55" s="41" t="inlineStr">
@@ -2171,14 +2179,14 @@
       </c>
       <c r="E55" s="43" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>PLA is now the PRIMARY AIRFRAME material (nose, both bay tubes, fins). 2 kg owned; buy 2 kg more for supports/reprints.</t>
         </is>
       </c>
       <c r="F55" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" s="45" t="n">
-        <v>36.99</v>
+        <v>19.99</v>
       </c>
       <c r="H55" s="45">
         <f>F55*G55</f>
@@ -2926,383 +2934,596 @@
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="33">
-      <c r="A78" s="46" t="inlineStr">
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>BMP388 barometric sensor (FLIGHT-BLOCKING - not in cart)</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>PID 3966</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>Apogee detect + the entire RQ3 coast-Cd reconstruction. Self-test gates on BARO_BMP.</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="H78" s="32">
+        <f>F78*G78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="33">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>Decoupling kit: 1000 uF + 100 uF low-ESR + SS34 Schottky</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>low-ESR + SS34</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>MANDATORY per COMPATIBILITY.md 5c - servo stall browns out the Pico without it.</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H79" s="32">
+        <f>F79*G79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="33">
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>SPDT slide arming switch (RBF sense on GP22)</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>SPDT slide</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr"/>
+      <c r="F80" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H80" s="32">
+        <f>F80*G80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="33">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>LiPo balance charger (2S)</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>HTRC B3</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>Cannot charge the OVONIC packs without one.</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H81" s="32">
+        <f>F81*G81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="33">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>Calibration masses to ~2.5 kg (Gate 4 load-cell cal)</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>known masses</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>UCEC set tops out at 211 g = 4% of the 5 kg axial cell's range.</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="H82" s="32">
+        <f>F82*G82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" s="33">
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>M2 ball-link rod ends, 10-pk (RE-SOURCED - original ships Aug 12-21)</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>B0F1XK7H11</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E83" s="32" t="inlineStr">
+        <is>
+          <t>Gimbal linkage sits on the Day-7 bench gate; original delivery misses it.</t>
+        </is>
+      </c>
+      <c r="F83" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="32" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H83" s="32">
+        <f>F83*G83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="46" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B78" s="47" t="n"/>
-      <c r="C78" s="47" t="n"/>
-      <c r="D78" s="47" t="inlineStr">
+      <c r="B84" s="47" t="n"/>
+      <c r="C84" s="47" t="n"/>
+      <c r="D84" s="47" t="inlineStr">
         <is>
           <t>https://www.adafruit.com/product/4543</t>
         </is>
       </c>
-      <c r="E78" s="47" t="n"/>
-      <c r="F78" s="47" t="n"/>
-      <c r="G78" s="47" t="n"/>
-      <c r="H78" s="48">
-        <f>SUM(H60:H77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="33">
-      <c r="D79" t="inlineStr">
+      <c r="E84" s="47" t="n"/>
+      <c r="F84" s="47" t="n"/>
+      <c r="G84" s="47" t="n"/>
+      <c r="H84" s="48">
+        <f>SUM(H60:H83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="33">
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>https://www.adafruit.com/product/5974</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="33">
-      <c r="A80" s="36" t="inlineStr">
+    <row r="86" ht="15" customHeight="1" s="33">
+      <c r="A86" s="36" t="inlineStr">
         <is>
           <t>8. Ground test - TVC balance + static stand (load cells + DAQ)</t>
         </is>
       </c>
-      <c r="B80" s="37" t="n"/>
-      <c r="C80" s="37" t="n"/>
-      <c r="D80" s="37" t="inlineStr">
+      <c r="B86" s="37" t="n"/>
+      <c r="C86" s="37" t="n"/>
+      <c r="D86" s="37" t="inlineStr">
         <is>
           <t>https://www.adafruit.com/product/5302</t>
         </is>
       </c>
-      <c r="E80" s="37" t="n"/>
-      <c r="F80" s="37" t="n"/>
-      <c r="G80" s="37" t="n"/>
-      <c r="H80" s="37" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="33">
-      <c r="A81" s="38" t="inlineStr">
+      <c r="E86" s="37" t="n"/>
+      <c r="F86" s="37" t="n"/>
+      <c r="G86" s="37" t="n"/>
+      <c r="H86" s="37" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="33">
+      <c r="A87" s="38" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B81" s="38" t="inlineStr">
+      <c r="B87" s="38" t="inlineStr">
         <is>
           <t>Storefront</t>
         </is>
       </c>
-      <c r="C81" s="38" t="inlineStr">
+      <c r="C87" s="38" t="inlineStr">
         <is>
           <t>Part # / Spec</t>
         </is>
       </c>
-      <c r="D81" s="38" t="inlineStr">
+      <c r="D87" s="38" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="E81" s="38" t="inlineStr">
+      <c r="E87" s="38" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F81" s="39" t="inlineStr">
+      <c r="F87" s="39" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G81" s="39" t="inlineStr">
+      <c r="G87" s="39" t="inlineStr">
         <is>
           <t>Unit ($)</t>
         </is>
       </c>
-      <c r="H81" s="39" t="inlineStr">
+      <c r="H87" s="39" t="inlineStr">
         <is>
           <t>Line ($)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="33">
-      <c r="A82" s="40" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="33">
+      <c r="A88" s="40" t="inlineStr">
         <is>
           <t>Adafruit strain-gauge load cell 1 kg (lateral X,Y)</t>
         </is>
       </c>
-      <c r="B82" s="41" t="inlineStr">
+      <c r="B88" s="41" t="inlineStr">
         <is>
           <t>Adafruit</t>
         </is>
       </c>
-      <c r="C82" s="41" t="inlineStr">
+      <c r="C88" s="41" t="inlineStr">
         <is>
           <t>PID 4540</t>
         </is>
       </c>
-      <c r="D82" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E82" s="43" t="inlineStr">
+      <c r="D88" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E88" s="43" t="inlineStr">
         <is>
           <t>in Adafruit cart</t>
         </is>
       </c>
-      <c r="F82" s="44" t="n">
+      <c r="F88" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G82" s="45" t="n">
+      <c r="G88" s="45" t="n">
         <v>3.95</v>
       </c>
-      <c r="H82" s="45">
-        <f>F82*G82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="33">
-      <c r="A83" s="40" t="inlineStr">
+      <c r="H88" s="45">
+        <f>F88*G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="33">
+      <c r="A89" s="40" t="inlineStr">
         <is>
           <t>Adafruit strain-gauge load cell 20 kg (static stand)</t>
         </is>
       </c>
-      <c r="B83" s="41" t="inlineStr">
+      <c r="B89" s="41" t="inlineStr">
         <is>
           <t>Adafruit</t>
         </is>
       </c>
-      <c r="C83" s="41" t="inlineStr">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>PID 4543</t>
         </is>
       </c>
-      <c r="D83" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E83" s="43" t="inlineStr">
+      <c r="D89" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E89" s="43" t="inlineStr">
         <is>
           <t>in Adafruit cart</t>
         </is>
       </c>
-      <c r="F83" s="44" t="n">
+      <c r="F89" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G83" s="45" t="n">
+      <c r="G89" s="45" t="n">
         <v>3.95</v>
       </c>
-      <c r="H83" s="45">
-        <f>F83*G83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="40" t="inlineStr">
+      <c r="H89" s="45">
+        <f>F89*G89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="33">
+      <c r="A90" s="40" t="inlineStr">
         <is>
           <t>Adafruit HX711 24-bit ADC</t>
         </is>
       </c>
-      <c r="B84" s="41" t="inlineStr">
+      <c r="B90" s="41" t="inlineStr">
         <is>
           <t>Adafruit</t>
         </is>
       </c>
-      <c r="C84" s="41" t="inlineStr">
+      <c r="C90" s="41" t="inlineStr">
         <is>
           <t>PID 5974</t>
         </is>
       </c>
-      <c r="D84" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E84" s="43" t="inlineStr">
+      <c r="D90" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E90" s="43" t="inlineStr">
         <is>
           <t>in Adafruit cart</t>
         </is>
       </c>
-      <c r="F84" s="44" t="n">
+      <c r="F90" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="G84" s="45" t="n">
+      <c r="G90" s="45" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="H84" s="45">
-        <f>F84*G84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="33">
-      <c r="A85" s="40" t="inlineStr">
+      <c r="H90" s="45">
+        <f>F90*G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="33">
+      <c r="A91" s="40" t="inlineStr">
         <is>
           <t>Adafruit KB2040 (RP2040) - spare/bench DAQ</t>
         </is>
       </c>
-      <c r="B85" s="41" t="inlineStr">
+      <c r="B91" s="41" t="inlineStr">
         <is>
           <t>Adafruit</t>
         </is>
       </c>
-      <c r="C85" s="41" t="inlineStr">
+      <c r="C91" s="41" t="inlineStr">
         <is>
           <t>PID 5302</t>
         </is>
       </c>
-      <c r="D85" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E85" s="43" t="inlineStr">
+      <c r="D91" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E91" s="43" t="inlineStr">
         <is>
           <t>FREE w/ order</t>
         </is>
       </c>
-      <c r="F85" s="44" t="n">
+      <c r="F91" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="G85" s="45" t="n">
+      <c r="G91" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="45">
-        <f>F85*G85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="33">
-      <c r="A86" s="40" t="inlineStr">
+      <c r="H91" s="45">
+        <f>F91*G91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="33">
+      <c r="A92" s="40" t="inlineStr">
         <is>
           <t>Digital load cell + HX711, 5 kg (2 sets) - axial Z</t>
         </is>
       </c>
-      <c r="B86" s="41" t="inlineStr">
+      <c r="B92" s="41" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C86" s="41" t="inlineStr">
+      <c r="C92" s="41" t="inlineStr">
         <is>
           <t>B09K7G3477</t>
         </is>
       </c>
-      <c r="D86" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E86" s="43" t="inlineStr">
+      <c r="D92" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E92" s="43" t="inlineStr">
         <is>
           <t>in cart</t>
         </is>
       </c>
-      <c r="F86" s="44" t="n">
+      <c r="F92" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="G86" s="45" t="n">
+      <c r="G92" s="45" t="n">
         <v>9.99</v>
       </c>
-      <c r="H86" s="45">
-        <f>F86*G86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="33">
-      <c r="A87" s="40" t="inlineStr">
+      <c r="H92" s="45">
+        <f>F92*G92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="33">
+      <c r="A93" s="40" t="inlineStr">
         <is>
           <t>UCEC calibration weight set 10 mg-100 g</t>
         </is>
       </c>
-      <c r="B87" s="41" t="inlineStr">
+      <c r="B93" s="41" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C87" s="41" t="inlineStr">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>B08R8RGCRS</t>
         </is>
       </c>
-      <c r="D87" s="42" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E87" s="43" t="inlineStr">
+      <c r="D93" s="42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E93" s="43" t="inlineStr">
         <is>
           <t>in cart</t>
         </is>
       </c>
-      <c r="F87" s="44" t="n">
+      <c r="F93" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="45" t="n">
+      <c r="G93" s="45" t="n">
         <v>9.99</v>
       </c>
-      <c r="H87" s="45">
-        <f>F87*G87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="33">
-      <c r="A88" s="46" t="inlineStr">
+      <c r="H93" s="45">
+        <f>F93*G93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="33">
+      <c r="A94" s="46" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B88" s="47" t="n"/>
-      <c r="C88" s="47" t="n"/>
-      <c r="D88" s="47" t="n"/>
-      <c r="E88" s="47" t="n"/>
-      <c r="F88" s="47" t="n"/>
-      <c r="G88" s="47" t="n"/>
-      <c r="H88" s="48">
-        <f>SUM(H82:H87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="33"/>
-    <row r="90" ht="15" customHeight="1" s="33">
-      <c r="A90" s="49" t="inlineStr">
+      <c r="B94" s="47" t="n"/>
+      <c r="C94" s="47" t="n"/>
+      <c r="D94" s="47" t="n"/>
+      <c r="E94" s="47" t="n"/>
+      <c r="F94" s="47" t="n"/>
+      <c r="G94" s="47" t="n"/>
+      <c r="H94" s="48">
+        <f>SUM(H88:H93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="33"/>
+    <row r="96">
+      <c r="A96" s="49" t="inlineStr">
         <is>
           <t>GROSS TO-BUY TOTAL</t>
         </is>
       </c>
-      <c r="B90" s="50" t="n"/>
-      <c r="C90" s="50" t="n"/>
-      <c r="D90" s="50" t="n"/>
-      <c r="E90" s="50" t="n"/>
-      <c r="F90" s="50" t="n"/>
-      <c r="G90" s="50" t="n"/>
-      <c r="H90" s="51">
-        <f>H11+H21+H29+H37+H47+H56+H78+H88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="33">
-      <c r="A91" s="52" t="inlineStr">
+      <c r="B96" s="50" t="n"/>
+      <c r="C96" s="50" t="n"/>
+      <c r="D96" s="50" t="n"/>
+      <c r="E96" s="50" t="n"/>
+      <c r="F96" s="50" t="n"/>
+      <c r="G96" s="50" t="n"/>
+      <c r="H96" s="51">
+        <f>H11+H21+H29+H37+H47+H56+H84+H94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="33">
+      <c r="A97" s="52" t="inlineStr">
         <is>
           <t>Less: Estes Pro Series II Launch Controller (reimbursed)</t>
         </is>
       </c>
-      <c r="H91" s="53">
+      <c r="H97" s="53">
         <f>-43.99</f>
         <v/>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="33">
-      <c r="A92" s="54" t="inlineStr">
+    <row r="98" ht="15" customHeight="1" s="33">
+      <c r="A98" s="54" t="inlineStr">
         <is>
           <t>NET OUT-OF-POCKET (still to buy)</t>
         </is>
       </c>
-      <c r="B92" s="50" t="n"/>
-      <c r="C92" s="50" t="n"/>
-      <c r="D92" s="50" t="n"/>
-      <c r="E92" s="50" t="n"/>
-      <c r="F92" s="50" t="n"/>
-      <c r="G92" s="50" t="n"/>
-      <c r="H92" s="55">
-        <f>H90+H91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="33"/>
-    <row r="94" ht="15" customHeight="1" s="33"/>
-    <row r="95" ht="15" customHeight="1" s="33"/>
-    <row r="97" ht="15" customHeight="1" s="33"/>
-    <row r="98" ht="15" customHeight="1" s="33"/>
+      <c r="B98" s="50" t="n"/>
+      <c r="C98" s="50" t="n"/>
+      <c r="D98" s="50" t="n"/>
+      <c r="E98" s="50" t="n"/>
+      <c r="F98" s="50" t="n"/>
+      <c r="G98" s="50" t="n"/>
+      <c r="H98" s="55">
+        <f>H96+H97</f>
+        <v/>
+      </c>
+    </row>
     <row r="99" ht="15" customHeight="1" s="33"/>
   </sheetData>
   <hyperlinks>
@@ -4375,7 +4596,7 @@
     <row r="8" ht="15" customHeight="1" s="33">
       <c r="A8" s="52" t="inlineStr">
         <is>
-          <t>6. Airframe filament (Amazon + Bambu ASA-Aero)</t>
+          <t>6. Airframe filament (PLA primary + PETG-CF owned)</t>
         </is>
       </c>
       <c r="B8" s="60">
@@ -4390,7 +4611,7 @@
         </is>
       </c>
       <c r="B9" s="60">
-        <f>BOM!H78</f>
+        <f>BOM!H84</f>
         <v/>
       </c>
     </row>
@@ -4401,7 +4622,7 @@
         </is>
       </c>
       <c r="B10" s="60">
-        <f>BOM!H88</f>
+        <f>BOM!H94</f>
         <v/>
       </c>
     </row>
@@ -4413,7 +4634,7 @@
         </is>
       </c>
       <c r="B12" s="62">
-        <f>BOM!H90</f>
+        <f>BOM!H96</f>
         <v/>
       </c>
     </row>
@@ -4435,7 +4656,7 @@
         </is>
       </c>
       <c r="B14" s="64">
-        <f>BOM!H92</f>
+        <f>BOM!H98</f>
         <v/>
       </c>
     </row>

--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="300">
   <si>
     <t xml:space="preserve">WYVERN-E - Master Bill of Materials</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t xml:space="preserve">B0CS6WXQPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09f: confirmed in cart ($19.99). Un-zeroed from earlier NOT IN CURRENT CART flag.</t>
   </si>
   <si>
     <t xml:space="preserve">Adafruit Perma-Proto half breadboard PCB</t>
@@ -2757,28 +2760,28 @@
         <v>14</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="H62" s="13" t="n">
         <f aca="false">F62*G62</f>
-        <v>0</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>14</v>
@@ -2799,13 +2802,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>14</v>
@@ -2826,13 +2829,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>14</v>
@@ -2853,13 +2856,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>14</v>
@@ -2880,13 +2883,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>14</v>
@@ -2907,13 +2910,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>14</v>
@@ -2934,13 +2937,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>14</v>
@@ -2961,13 +2964,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>14</v>
@@ -2988,19 +2991,19 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
@@ -3015,19 +3018,19 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
@@ -3042,13 +3045,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>14</v>
@@ -3069,13 +3072,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>14</v>
@@ -3096,13 +3099,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>14</v>
@@ -3123,13 +3126,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>14</v>
@@ -3150,13 +3153,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>14</v>
@@ -3177,7 +3180,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>17</v>
@@ -3189,7 +3192,7 @@
         <v>14</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>2</v>
@@ -3204,19 +3207,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>1</v>
@@ -3231,19 +3234,19 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>2</v>
@@ -3258,19 +3261,19 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>1</v>
@@ -3285,19 +3288,19 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>1</v>
@@ -3312,19 +3315,19 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>1</v>
@@ -3344,29 +3347,29 @@
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
       <c r="D84" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E84" s="15"/>
       <c r="F84" s="15"/>
       <c r="G84" s="15"/>
       <c r="H84" s="16" t="n">
         <f aca="false">SUM(H60:H83)</f>
-        <v>1.5</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
@@ -3401,19 +3404,19 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F88" s="12" t="n">
         <v>2</v>
@@ -3428,19 +3431,19 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F89" s="12" t="n">
         <v>2</v>
@@ -3455,19 +3458,19 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>3</v>
@@ -3482,13 +3485,13 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>14</v>
@@ -3509,19 +3512,19 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F92" s="12" t="n">
         <v>1</v>
@@ -3536,13 +3539,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>14</v>
@@ -3579,7 +3582,7 @@
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
@@ -3589,12 +3592,12 @@
       <c r="G96" s="18"/>
       <c r="H96" s="19" t="n">
         <f aca="false">H11+H21+H29+H37+H47+H56+H84+H94+H111+H124</f>
-        <v>1181.59</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H97" s="21" t="n">
         <f aca="false">-39.6</f>
@@ -3603,7 +3606,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B98" s="18"/>
       <c r="C98" s="18"/>
@@ -3613,13 +3616,13 @@
       <c r="G98" s="18"/>
       <c r="H98" s="23" t="n">
         <f aca="false">H96+H97</f>
-        <v>1141.99</v>
+        <v>1161.98</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3650,19 +3653,19 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>3</v>
@@ -3677,13 +3680,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>14</v>
@@ -3704,13 +3707,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>14</v>
@@ -3731,19 +3734,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F105" s="1" t="n">
         <v>2</v>
@@ -3758,19 +3761,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F106" s="1" t="n">
         <v>2</v>
@@ -3785,19 +3788,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F107" s="1" t="n">
         <v>2</v>
@@ -3812,19 +3815,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F108" s="1" t="n">
         <v>1</v>
@@ -3839,13 +3842,13 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>14</v>
@@ -3866,19 +3869,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F110" s="1" t="n">
         <v>4</v>
@@ -3902,7 +3905,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3933,19 +3936,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F115" s="1" t="n">
         <v>1</v>
@@ -3960,19 +3963,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F116" s="1" t="n">
         <v>1</v>
@@ -3987,19 +3990,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F117" s="1" t="n">
         <v>1</v>
@@ -4014,19 +4017,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>1</v>
@@ -4041,19 +4044,19 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="F119" s="1" t="n">
         <v>1</v>
@@ -4068,19 +4071,19 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F120" s="1" t="n">
         <v>1</v>
@@ -4095,19 +4098,19 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F121" s="1" t="n">
         <v>1</v>
@@ -4122,19 +4125,19 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>1</v>
@@ -4149,19 +4152,19 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F123" s="1" t="n">
         <v>1</v>
@@ -4263,7 +4266,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4286,7 +4289,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>10</v>
@@ -4294,13 +4297,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>6</v>
@@ -4319,13 +4322,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>6</v>
@@ -4344,13 +4347,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>6</v>
@@ -4369,19 +4372,19 @@
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>3</v>
@@ -4396,19 +4399,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>1</v>
@@ -4423,13 +4426,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>6</v>
@@ -4448,13 +4451,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>6</v>
@@ -4473,19 +4476,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>1</v>
@@ -4500,13 +4503,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>6</v>
@@ -4525,13 +4528,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>6</v>
@@ -4550,19 +4553,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>1</v>
@@ -4577,13 +4580,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>6</v>
@@ -4602,19 +4605,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -4629,19 +4632,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>2</v>
@@ -4656,19 +4659,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>2</v>
@@ -4683,19 +4686,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>1</v>
@@ -4710,19 +4713,19 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>4</v>
@@ -4737,19 +4740,19 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>3</v>
@@ -4764,19 +4767,19 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
@@ -4791,19 +4794,19 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>1</v>
@@ -4818,19 +4821,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>6</v>
@@ -4845,19 +4848,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -4872,19 +4875,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>6</v>
@@ -4899,7 +4902,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -4962,7 +4965,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5025,12 +5028,12 @@
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">BOM!H84</f>
-        <v>1.5</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B10" s="28" t="n">
         <f aca="false">BOM!H94</f>
@@ -5039,7 +5042,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">BOM!H111</f>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B12" s="1" t="n">
         <f aca="false">BOM!H124</f>
@@ -5057,16 +5060,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">BOM!H96</f>
-        <v>1181.59</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B14" s="21" t="n">
         <f aca="false">-39.6</f>
@@ -5075,17 +5078,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">BOM!H98</f>
-        <v>1141.99</v>
+        <v>1161.98</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">'Already Acquired'!H27</f>
@@ -5094,11 +5097,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">B15+B17</f>
-        <v>1621.26</v>
+        <v>1641.25</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -588,7 +588,7 @@
     <t xml:space="preserve">RP2350B flight computer board</t>
   </si>
   <si>
-    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $195 total for 3 fabricated boards.</t>
+    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $200 total for 3 fabricated boards (updated 2026-08-10, was $195); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
   </si>
   <si>
     <t xml:space="preserve">eMagTech F-F servo extension cable 10cm (10-pk)</t>
@@ -3592,7 +3592,7 @@
       <c r="G96" s="18"/>
       <c r="H96" s="19" t="n">
         <f aca="false">H11+H21+H29+H37+H47+H56+H84+H94+H111+H124</f>
-        <v>1201.58</v>
+        <v>1206.58</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3616,7 +3616,7 @@
       <c r="G98" s="18"/>
       <c r="H98" s="23" t="n">
         <f aca="false">H96+H97</f>
-        <v>1161.98</v>
+        <v>1166.98</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3671,11 +3671,11 @@
         <v>3</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>65</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="H102" s="1" t="n">
         <f aca="false">F102*G102</f>
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="H111" s="1" t="n">
         <f aca="false">SUM(H102:H110)</f>
-        <v>288.43</v>
+        <v>293.43</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">BOM!H111</f>
-        <v>288.43</v>
+        <v>293.43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">BOM!H96</f>
-        <v>1201.58</v>
+        <v>1206.58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">BOM!H98</f>
-        <v>1161.98</v>
+        <v>1166.98</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">B15+B17</f>
-        <v>1641.25</v>
+        <v>1646.25</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -588,7 +588,7 @@
     <t xml:space="preserve">RP2350B flight computer board</t>
   </si>
   <si>
-    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $200 total for 3 fabricated boards (updated 2026-08-10, was $195); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
+    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $207.01 total for 3 fabricated boards (updated 2026-08-11, was $200); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
   </si>
   <si>
     <t xml:space="preserve">eMagTech F-F servo extension cable 10cm (10-pk)</t>
@@ -3592,7 +3592,7 @@
       <c r="G96" s="18"/>
       <c r="H96" s="19" t="n">
         <f aca="false">H11+H21+H29+H37+H47+H56+H84+H94+H111+H124</f>
-        <v>1206.58</v>
+        <v>1213.59</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3616,7 +3616,7 @@
       <c r="G98" s="18"/>
       <c r="H98" s="23" t="n">
         <f aca="false">H96+H97</f>
-        <v>1166.98</v>
+        <v>1173.99</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3671,11 +3671,11 @@
         <v>3</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>66.6666666666667</v>
+        <v>69.0033333333333</v>
       </c>
       <c r="H102" s="1" t="n">
         <f aca="false">F102*G102</f>
-        <v>200</v>
+        <v>207.01</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="H111" s="1" t="n">
         <f aca="false">SUM(H102:H110)</f>
-        <v>293.43</v>
+        <v>300.44</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">BOM!H111</f>
-        <v>293.43</v>
+        <v>300.44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">BOM!H96</f>
-        <v>1206.58</v>
+        <v>1213.59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">BOM!H98</f>
-        <v>1166.98</v>
+        <v>1173.99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">B15+B17</f>
-        <v>1646.25</v>
+        <v>1653.26</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -22,9 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="300">
-  <si>
-    <t xml:space="preserve">WYVERN-E - Master Bill of Materials</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="301">
+  <si>
+    <t xml:space="preserve">GTR70E WYVERN - Master Bill of Materials</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-09: BOM to-buy total now reflects ONLY items in the 3 live carts (Amazon $252.93, Adafruit $95.10, Estes $325.01) plus the $175 custom PCB - everything else zeroed from cost (kept as line items, flagged "NOT IN CURRENT CART") except airframe filament (Section 6), which is kept per explicit exception. ⚠ This includes the F15-4 flight motor (row 41) and E16-4 commissioning motors (row 43) - zeroed from cost because they are not in these carts, not because they are unneeded.</t>
@@ -129,6 +129,9 @@
     <t xml:space="preserve">Hobbywing B008ZNWOYY</t>
   </si>
   <si>
+    <t xml:space="preserve">NOT NEEDED (2026-08-12): PCB1's onboard TPS564201 buck already regulates 2S -&gt; ~5V for the Pico/servos -- this discrete UBEC would be a redundant second regulator. Drop from cart; keep row for history only.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HTRC B3 2S-3S LiPo balance charger</t>
   </si>
   <si>
@@ -579,7 +582,7 @@
     <t xml:space="preserve">9. 2026-08-09 Cart Reconciliation &amp; Custom PCB</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom PCB fabrication (JLCPCB) - WYVERN-E flight computer, 3 boards</t>
+    <t xml:space="preserve">Custom PCB fabrication (JLCPCB) - GTR70E WYVERN flight computer, 3 boards</t>
   </si>
   <si>
     <t xml:space="preserve">JLCPCB</t>
@@ -588,7 +591,7 @@
     <t xml:space="preserve">RP2350B flight computer board</t>
   </si>
   <si>
-    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $207.01 total for 3 fabricated boards (updated 2026-08-11, was $200); one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
+    <t xml:space="preserve">DFM-reviewed Gerber submission (soldermask/silkscreen/SMT placement flags addressed). $231.72 total for 3 fabricated boards (updated 2026-08-12, was $207.01) -- board grew from Ø61mm to Ø62mm and gained parts (65 components vs 61) to fit the larger SS-12D10-G5 switch; one of the three is earmarked for the ground servo TVC test stand rather than flight/spare use.</t>
   </si>
   <si>
     <t xml:space="preserve">eMagTech F-F servo extension cable 10cm (10-pk)</t>
@@ -909,7 +912,7 @@
     <t xml:space="preserve">Total already paid</t>
   </si>
   <si>
-    <t xml:space="preserve">WYVERN-E - BOM Summary</t>
+    <t xml:space="preserve">GTR70E WYVERN - BOM Summary</t>
   </si>
   <si>
     <t xml:space="preserve">Gross to-buy total</t>
@@ -1795,7 +1798,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -1810,19 +1813,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>1</v>
@@ -1837,13 +1840,13 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>14</v>
@@ -1864,13 +1867,13 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>14</v>
@@ -1891,13 +1894,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>14</v>
@@ -1933,7 +1936,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1971,19 +1974,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -1998,19 +2001,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>2</v>
@@ -2025,19 +2028,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>2</v>
@@ -2052,19 +2055,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -2094,7 +2097,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2132,19 +2135,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>1</v>
@@ -2159,13 +2162,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>14</v>
@@ -2184,19 +2187,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>1</v>
@@ -2211,19 +2214,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>1</v>
@@ -2253,7 +2256,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2291,19 +2294,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>2</v>
@@ -2318,19 +2321,19 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>5</v>
@@ -2345,19 +2348,19 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>3</v>
@@ -2372,19 +2375,19 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>1</v>
@@ -2399,19 +2402,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>81</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>5</v>
@@ -2426,19 +2429,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
@@ -2468,7 +2471,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2506,19 +2509,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>1</v>
@@ -2533,19 +2536,19 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F52" s="12" t="n">
         <v>1</v>
@@ -2560,19 +2563,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
@@ -2587,19 +2590,19 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
@@ -2614,19 +2617,19 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
@@ -2656,7 +2659,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2694,13 +2697,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>14</v>
@@ -2721,13 +2724,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>14</v>
@@ -2748,19 +2751,19 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -2775,13 +2778,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>14</v>
@@ -2802,13 +2805,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>14</v>
@@ -2829,13 +2832,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>14</v>
@@ -2856,13 +2859,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>14</v>
@@ -2883,13 +2886,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>14</v>
@@ -2910,13 +2913,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>14</v>
@@ -2937,13 +2940,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>14</v>
@@ -2964,13 +2967,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>14</v>
@@ -2991,19 +2994,19 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
@@ -3018,19 +3021,19 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
@@ -3045,13 +3048,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>14</v>
@@ -3072,13 +3075,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>14</v>
@@ -3099,13 +3102,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>14</v>
@@ -3126,13 +3129,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>14</v>
@@ -3153,13 +3156,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>14</v>
@@ -3180,7 +3183,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>17</v>
@@ -3192,7 +3195,7 @@
         <v>14</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>2</v>
@@ -3207,19 +3210,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>1</v>
@@ -3234,19 +3237,19 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>2</v>
@@ -3261,19 +3264,19 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>1</v>
@@ -3288,19 +3291,19 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>1</v>
@@ -3315,19 +3318,19 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>1</v>
@@ -3347,7 +3350,7 @@
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
       <c r="D84" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E84" s="15"/>
       <c r="F84" s="15"/>
@@ -3359,17 +3362,17 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D85" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
@@ -3404,19 +3407,19 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F88" s="12" t="n">
         <v>2</v>
@@ -3431,19 +3434,19 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F89" s="12" t="n">
         <v>2</v>
@@ -3458,19 +3461,19 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>3</v>
@@ -3485,13 +3488,13 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>14</v>
@@ -3512,19 +3515,19 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F92" s="12" t="n">
         <v>1</v>
@@ -3539,19 +3542,19 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F93" s="12" t="n">
         <v>1</v>
@@ -3582,7 +3585,7 @@
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
@@ -3592,12 +3595,12 @@
       <c r="G96" s="18"/>
       <c r="H96" s="19" t="n">
         <f aca="false">H11+H21+H29+H37+H47+H56+H84+H94+H111+H124</f>
-        <v>1213.59</v>
+        <v>1238.3</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H97" s="21" t="n">
         <f aca="false">-39.6</f>
@@ -3606,7 +3609,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B98" s="18"/>
       <c r="C98" s="18"/>
@@ -3616,13 +3619,13 @@
       <c r="G98" s="18"/>
       <c r="H98" s="23" t="n">
         <f aca="false">H96+H97</f>
-        <v>1173.99</v>
+        <v>1198.7</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3653,46 +3656,46 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>3</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>69.0033333333333</v>
+        <v>77.24</v>
       </c>
       <c r="H102" s="1" t="n">
         <f aca="false">F102*G102</f>
-        <v>207.01</v>
+        <v>231.72</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>1</v>
@@ -3707,19 +3710,19 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F104" s="1" t="n">
         <v>1</v>
@@ -3734,19 +3737,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F105" s="1" t="n">
         <v>2</v>
@@ -3761,19 +3764,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F106" s="1" t="n">
         <v>2</v>
@@ -3788,19 +3791,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F107" s="1" t="n">
         <v>2</v>
@@ -3815,19 +3818,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" s="1" t="n">
         <v>1</v>
@@ -3842,19 +3845,19 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F109" s="1" t="n">
         <v>1</v>
@@ -3869,19 +3872,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F110" s="1" t="n">
         <v>4</v>
@@ -3900,12 +3903,12 @@
       </c>
       <c r="H111" s="1" t="n">
         <f aca="false">SUM(H102:H110)</f>
-        <v>300.44</v>
+        <v>325.15</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3936,19 +3939,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F115" s="1" t="n">
         <v>1</v>
@@ -3963,19 +3966,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F116" s="1" t="n">
         <v>1</v>
@@ -3990,19 +3993,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F117" s="1" t="n">
         <v>1</v>
@@ -4017,19 +4020,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>1</v>
@@ -4044,19 +4047,19 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="F119" s="1" t="n">
         <v>1</v>
@@ -4071,19 +4074,19 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F120" s="1" t="n">
         <v>1</v>
@@ -4098,19 +4101,19 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F121" s="1" t="n">
         <v>1</v>
@@ -4125,19 +4128,19 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>1</v>
@@ -4152,19 +4155,19 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F123" s="1" t="n">
         <v>1</v>
@@ -4266,7 +4269,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4289,7 +4292,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>10</v>
@@ -4297,13 +4300,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>6</v>
@@ -4322,13 +4325,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>6</v>
@@ -4347,13 +4350,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>6</v>
@@ -4372,19 +4375,19 @@
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>3</v>
@@ -4399,19 +4402,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>1</v>
@@ -4426,13 +4429,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>6</v>
@@ -4451,13 +4454,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>6</v>
@@ -4476,19 +4479,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>1</v>
@@ -4503,13 +4506,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>6</v>
@@ -4528,13 +4531,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>6</v>
@@ -4553,19 +4556,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>1</v>
@@ -4580,13 +4583,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>6</v>
@@ -4605,19 +4608,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -4632,19 +4635,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>2</v>
@@ -4659,19 +4662,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>2</v>
@@ -4686,19 +4689,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>1</v>
@@ -4713,19 +4716,19 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>4</v>
@@ -4740,19 +4743,19 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>3</v>
@@ -4767,19 +4770,19 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
@@ -4794,19 +4797,19 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>1</v>
@@ -4821,19 +4824,19 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>6</v>
@@ -4848,19 +4851,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -4875,19 +4878,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>6</v>
@@ -4902,7 +4905,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -4965,7 +4968,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4988,7 +4991,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">BOM!H29</f>
@@ -4997,7 +5000,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">BOM!H37</f>
@@ -5006,7 +5009,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">BOM!H47</f>
@@ -5015,7 +5018,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">BOM!H56</f>
@@ -5024,7 +5027,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">BOM!H84</f>
@@ -5033,7 +5036,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B10" s="28" t="n">
         <f aca="false">BOM!H94</f>
@@ -5042,16 +5045,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" s="1" t="n">
         <f aca="false">BOM!H111</f>
-        <v>300.44</v>
+        <v>325.15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B12" s="1" t="n">
         <f aca="false">BOM!H124</f>
@@ -5060,16 +5063,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">BOM!H96</f>
-        <v>1213.59</v>
+        <v>1238.3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B14" s="21" t="n">
         <f aca="false">-39.6</f>
@@ -5078,17 +5081,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">BOM!H98</f>
-        <v>1173.99</v>
+        <v>1198.7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">'Already Acquired'!H27</f>
@@ -5097,11 +5100,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">B15+B17</f>
-        <v>1653.26</v>
+        <v>1677.97</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/WYVERN_E4_BOM.xlsx
+++ b/Documentation/WYVERN_E4_BOM.xlsx
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="50" customWidth="1" style="33" min="1" max="1"/>
@@ -673,10 +673,11 @@
     <row r="2" ht="15" customHeight="1" s="34">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>Pico 2 W perfboard revision: the custom PCB1 fab line is retired (row 102 zeroed). Flight computer is a Raspberry Pi Pico 2 W on a generic 20x24 perfboard; power is a discrete 5 V switching UBEC. See Documentation/CANONICAL_NUMBERS.md.</t>
-        </is>
-      </c>
-    </row>
+          <t>Reconciled 2026-08-14 against the live Amazon cart (25 items, $593.92 list / $582.37 after coupons) and the live Adafruit cart ($216.95). Pico 2 W perfboard revision; custom PCB1 fab retired. ABS dropped from RQ2 and from procurement. Three-point-bend rig cancelled, 20 kg load cell dropped. Lines reading NOT IN EITHER CART are zeroed from the to-buy total but are still required hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="34">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -736,17 +737,17 @@
     <row r="6" ht="23.25" customHeight="1" s="34">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Raspberry Pi Pico 2 W (pre-soldered header) - flight FC + spare</t>
+          <t>Raspberry Pi Pico 2 W (pre-soldered header) - flight FC + ground-stand FC</t>
         </is>
       </c>
       <c r="B6" s="42" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>B0DP54FWX1</t>
+          <t>PID 6087</t>
         </is>
       </c>
       <c r="D6" s="43" t="inlineStr">
@@ -756,14 +757,14 @@
       </c>
       <c r="E6" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09e: IS in live Amazon cart ($16.31, qty1 - corrected from qty2). Contradicts earlier "superseded, not being bought" note - real cart wins. Role unclear (bench/dev spare alongside custom RP2350B PCB, or KB2040 replacement) - confirm intended use before assuming it is flight hardware.</t>
+          <t>2026-08-13: RE-SOURCED from Amazon B0DP54FWX1 ($16.31) to Adafruit PID 6087 ($7.00 ea); qty2 in the live Adafruit cart. Two boards = flight FC + ground TVC stand FC, both running the same image (stand built with -DWYVERN_GROUND_TEST=1).</t>
         </is>
       </c>
       <c r="F6" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="46" t="n">
-        <v>16.31</v>
+        <v>7</v>
       </c>
       <c r="H6" s="46">
         <f>F6*G6</f>
@@ -773,7 +774,7 @@
     <row r="7" ht="15" customHeight="1" s="34">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>BNO085 9-DOF IMU x2 (bay 0x4B, gimbal 0x4A)</t>
+          <t>BNO085 9-DOF IMU x4 (bay 0x4B, flight gimbal 0x4A, ground rig, spare)</t>
         </is>
       </c>
       <c r="B7" s="42" t="inlineStr">
@@ -793,11 +794,11 @@
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>TWO required: bay unit DI-&gt;3V3 gives 0x4B, gimbal unit default 0x4A. Both on the shared I2C bus.</t>
+          <t>FOUR units, confirmed 2026-08-14: (1) electronics bay 0x4B, DI-&gt;3V3; (2) flight TVC gimbal 0x4A, default; (3) ground servo test rig gimbal, so the flight unit never has to be un/re-mounted between bench and vehicle; (4) spare. The flight gimbal unit crosses the separation joint on pull-apart leads and is the most damage-exposed sensor on the vehicle.</t>
         </is>
       </c>
       <c r="F7" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="46" t="n">
         <v>29.5</v>
@@ -830,14 +831,14 @@
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>Backup baro at 0x77 (SDO unconnected). BME688 already acquired covers 0x76 primary.</t>
+          <t>2026-08-13: qty1 in the live Adafruit cart at $9.95 (previously zeroed). PRIMARY altimeter at 0x77, SDO unconnected. BME688 (Already Acquired) is redundant pressure + environmental at 0x76. Row 80 is the zeroed duplicate. NOTE: baro.h / wyvern_config.h still treat BME688 as primary - firmware needs to swap to match the proposal.</t>
         </is>
       </c>
       <c r="F8" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="46" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H8" s="46">
         <f>F8*G8</f>
@@ -884,7 +885,7 @@
     <row r="10" ht="15" customHeight="1" s="34">
       <c r="A10" s="41" t="inlineStr">
         <is>
-          <t>Liaoan USB-A/USB-C 3.0 OTG adapter set (6 pc)</t>
+          <t>USB-A/USB-C 3.0 OTG adapter set - NOT NEEDED</t>
         </is>
       </c>
       <c r="B10" s="42" t="inlineStr">
@@ -904,11 +905,11 @@
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>DROPPED 2026-08-14, confirmed not needed. The USB-C microSD card reader in Already Acquired covers both the flight log and the i3 camera card.</t>
         </is>
       </c>
       <c r="F10" s="45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="46" t="n">
         <v>0</v>
@@ -935,6 +936,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="37" t="inlineStr">
         <is>
@@ -994,7 +996,7 @@
     <row r="15" ht="15" customHeight="1" s="34">
       <c r="A15" s="41" t="inlineStr">
         <is>
-          <t>Zeee 2S 7.4 V 450 mAh LiPo (4-pk) - light flight pack</t>
+          <t>OVONIC 2S 7.6 V 450 mAh 100C LiPo, XT30 (2-pack) - flight pack + spare</t>
         </is>
       </c>
       <c r="B15" s="42" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="C15" s="42" t="inlineStr">
         <is>
-          <t>OVONIC B0D3F5SQ5T</t>
+          <t>B0D3F5SQ5T</t>
         </is>
       </c>
       <c r="D15" s="43" t="inlineStr">
@@ -1014,14 +1016,14 @@
       </c>
       <c r="E15" s="44" t="inlineStr">
         <is>
-          <t>in cart; 2-pack ~7.6V 450mAh 2S w/ XT30 (replaces Zeee)</t>
+          <t>2026-08-13: $20.37 list, $10.18 after coupon. Two packs per order = flight + spare. 100C on 450 mAh is 45 A burst against the ~1.9 A the servos + UBEC actually pull. XT30 feeds PPTC -&gt; arming switch -&gt; UBEC.</t>
         </is>
       </c>
       <c r="F15" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="46" t="n">
-        <v>14.25</v>
+        <v>10.18</v>
       </c>
       <c r="H15" s="46">
         <f>F15*G15</f>
@@ -1051,7 +1053,7 @@
       </c>
       <c r="E16" s="44" t="inlineStr">
         <is>
-          <t>REQUIRED (Pico 2 W revision): no onboard buck any more. 2S -&gt; 5 V for Pico VSYS + servo rail. Must be switching.</t>
+          <t>*** FLIGHT-BLOCKING GAP: NOT IN EITHER CART (2026-08-13). *** PCB1 is retired, so there is no onboard buck - the Pico VSYS and the servo rail have nothing to run from without this. Order first. Must be 5 V 3 A SWITCHING; a linear BEC dissipating 2S down to 5 V at 1.9 A will cook.</t>
         </is>
       </c>
       <c r="F16" s="45" t="n">
@@ -1105,7 +1107,7 @@
     <row r="18" ht="23.25" customHeight="1" s="34">
       <c r="A18" s="41" t="inlineStr">
         <is>
-          <t>Bulk cap 470 uF 10 V electrolytic + 100 nF ceramic</t>
+          <t>Bulk cap 470 uF 10 V + 100 nF ceramic (ON HAND - see Already Acquired)</t>
         </is>
       </c>
       <c r="B18" s="42" t="inlineStr">
@@ -1125,11 +1127,11 @@
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>470 uF at the servo feed absorbs stall transients that would brown out the Pico. 100 nF on the ADC tap.</t>
+          <t>ALREADY ACQUIRED 2026-08-14, zeroed here to avoid double-counting. 470 uF at the servo feed absorbs stall transients that would brown out the Pico through the shared 5 V rail; 100 nF on the ADC divider tap.</t>
         </is>
       </c>
       <c r="F18" s="45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="46" t="n">
         <v>0</v>
@@ -1142,7 +1144,7 @@
     <row r="19" ht="23.25" customHeight="1" s="34">
       <c r="A19" s="41" t="inlineStr">
         <is>
-          <t>100 kohm / 47 kohm 1% resistor pack (battery divider)</t>
+          <t>100 kohm / 47 kohm 1% resistors (ON HAND - see Already Acquired)</t>
         </is>
       </c>
       <c r="B19" s="42" t="inlineStr">
@@ -1162,11 +1164,11 @@
       </c>
       <c r="E19" s="44" t="inlineStr">
         <is>
-          <t>100k/47k divider from armed pack to GP26: 2.686 V at 8.4 V, 1.918 V at the 6.0 V cutoff.</t>
+          <t>ALREADY ACQUIRED 2026-08-14, zeroed here. Battery divider to GP26. Values are hard-coded as WYV_VBAT_DIV_TOP/BOT in wyvern_config.h - confirm the on-hand parts are actually 100k and 47k before soldering, or the cutoffs shift.</t>
         </is>
       </c>
       <c r="F19" s="45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="46" t="n">
         <v>0</v>
@@ -1179,7 +1181,7 @@
     <row r="20" ht="15" customHeight="1" s="34">
       <c r="A20" s="41" t="inlineStr">
         <is>
-          <t>Arming switch, 20 A class (nose-cone access)</t>
+          <t>DaierTek 20 mm SPST round rocker arming switch, UL-listed (5-pack)</t>
         </is>
       </c>
       <c r="B20" s="42" t="inlineStr">
@@ -1189,7 +1191,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t>SPDT slide switch</t>
+          <t>B07S1MV462</t>
         </is>
       </c>
       <c r="D20" s="43" t="inlineStr">
@@ -1199,14 +1201,14 @@
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
-          <t>Carries full pack current ~1.9 A plus UBEC/bulk inrush. Reached by pulling the nose cone, no airframe penetration.</t>
+          <t>2026-08-13: KCD1, 20 A class. Carries full pack current (~1.9 A) plus UBEC and bulk-cap inrush, so the rating is large margin. Mounted inside the Upper BT and reached by pulling the nose cone, not through the skin. 5-pack covers flight + both ground stands + spares.</t>
         </is>
       </c>
       <c r="F20" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="46" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="H20" s="46">
         <f>F20*G20</f>
@@ -1230,6 +1232,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="34">
       <c r="A23" s="37" t="inlineStr">
         <is>
@@ -1346,7 +1349,7 @@
       </c>
       <c r="E26" s="44" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>2026-08-13: qty2 in cart = 20 bearings. Gimbal uses 4 (two per axis); rest are spares and ground-rig stock.</t>
         </is>
       </c>
       <c r="F26" s="45" t="n">
@@ -1363,7 +1366,7 @@
     <row r="27" ht="15" customHeight="1" s="34">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>uxcell M2 15 mm linkage rod-end ball joint (4 PCS)</t>
+          <t>uxcell M2 / 15 mm linkage tie rod end ball head joint (4 pcs, red)</t>
         </is>
       </c>
       <c r="B27" s="42" t="inlineStr">
@@ -1373,7 +1376,7 @@
       </c>
       <c r="C27" s="42" t="inlineStr">
         <is>
-          <t>B07Q2V3R61</t>
+          <t>B07Q2WHMWK</t>
         </is>
       </c>
       <c r="D27" s="43" t="inlineStr">
@@ -1383,7 +1386,7 @@
       </c>
       <c r="E27" s="44" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>RE-SOURCED 2026-08-14 (final): B07Q2WHMWK is the same uxcell M2 x 15 mm rod end as the original B07Q2V3R61, red instead of blue, 4 pcs per pack, in stock. qty2 = 8 rod ends against the 2 the gimbal needs. GEOMETRY RESTORED: 15 mm, so the earlier 19 mm pushrod-length concern is void and the original linkage sizing stands. Verify the cart price against $12.99 at checkout.</t>
         </is>
       </c>
       <c r="F27" s="45" t="n">
@@ -1420,7 +1423,7 @@
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>2026-08-13: qty1 in cart. Doubles as the M-F extension stock for the servo signal and power leads that part at the bulkhead on ejection.</t>
         </is>
       </c>
       <c r="F28" s="45" t="n">
@@ -1451,6 +1454,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="34">
       <c r="A31" s="37" t="inlineStr">
         <is>
@@ -1668,6 +1672,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="15" customHeight="1" s="34">
       <c r="A39" s="37" t="inlineStr">
         <is>
@@ -1727,7 +1732,7 @@
     <row r="41" ht="15" customHeight="1" s="34">
       <c r="A41" s="41" t="inlineStr">
         <is>
-          <t>Estes F15-4 2-ct (flight; 4 s delay + ejection = recovery)</t>
+          <t>Estes F15-4 2-ct (flight motor; 4 s delay + ejection = recovery)</t>
         </is>
       </c>
       <c r="B41" s="42" t="inlineStr">
@@ -1747,14 +1752,14 @@
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
-          <t>⚠ FLIGHT MOTOR - NOT IN CURRENT CART (2026-08-09). Zeroed from to-buy total per cart-only policy, but this is the actual flight motor - confirm separately before assuming it's covered.</t>
+          <t>2026-08-14: one 2-ct pack added to the cart, and 2 motors are already on hand (see Already Acquired). Total 4 flight motors, which matches the F15-4 count in WYVERN_E4_GSE_TestStands.md section 5. Verify the Estes cart price - $33.99 is carried across from the F15-0 line.</t>
         </is>
       </c>
       <c r="F41" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="46" t="n">
-        <v>0</v>
+        <v>33.99</v>
       </c>
       <c r="H41" s="46">
         <f>F41*G41</f>
@@ -1963,10 +1968,11 @@
         <v/>
       </c>
     </row>
+    <row r="48"/>
     <row r="49" ht="15" customHeight="1" s="34">
       <c r="A49" s="37" t="inlineStr">
         <is>
-          <t>6. Airframe filament (Amazon + Bambu Lab - see flag notes, scope mismatch vs PLA/PETG-CF design)</t>
+          <t>6. Airframe filament (Amazon + Bambu Lab; ASA-Aero / PETG-CF / PC-FR fly, the rest are RQ2 comparison + tooling)</t>
         </is>
       </c>
       <c r="B49" s="38" t="n"/>
@@ -2042,7 +2048,7 @@
       </c>
       <c r="E51" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09b: real Amazon cart item (swapped from Bambu Lab sourcing). WARNING - this material was struck from the design scope in 2026-08b (PC-FR/ASA-Aero/ABS/PC coupon-testing program dropped; PLA+PETG-CF are the only current airframe materials, see CONFLICTS.md sec7 and BUILD_READINESS.md sec2). Confirm this purchase is intentional (reserve stock / RQ2 baseline archive) rather than assumed as a current flight-part material.</t>
+          <t>2026-08-13: in cart at $49.99. UL94 V0 halogen-free PC-FR - this is the TVC assembly material (motor mount, gimbal). White, not black; cosmetic only.</t>
         </is>
       </c>
       <c r="F51" s="45" t="n">
@@ -2079,7 +2085,7 @@
       </c>
       <c r="E52" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09: real Bambu Lab cart item. WARNING - this material was struck from the design scope in 2026-08b (PC-FR/ASA-Aero/ABS/PC coupon-testing program dropped; PLA+PETG-CF are the only current airframe materials, see CONFLICTS.md sec7 and BUILD_READINESS.md sec2). Confirm this purchase is intentional (reserve stock / RQ2 baseline archive) rather than assumed as a current flight-part material.</t>
+          <t>2026-08-13: Bambu Lab store item, NOT in either cart pasted today (Bambu is a separate storefront). Still required - ASA-Aero is the upper and lower body tube material. Amazon equivalent B0C9RC7SJG if you want off Bambu.</t>
         </is>
       </c>
       <c r="F52" s="45" t="n">
@@ -2096,7 +2102,7 @@
     <row r="53" ht="15" customHeight="1" s="34">
       <c r="A53" s="41" t="inlineStr">
         <is>
-          <t>eSUN ABS+ Filament (Black), Amazon - 1 kg</t>
+          <t>eSUN ABS+ Filament (Black) - DROPPED</t>
         </is>
       </c>
       <c r="B53" s="42" t="inlineStr">
@@ -2116,14 +2122,14 @@
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09b: real Amazon cart item (swapped from Bambu Lab sourcing). WARNING - this material was struck from the design scope in 2026-08b (PC-FR/ASA-Aero/ABS/PC coupon-testing program dropped; PLA+PETG-CF are the only current airframe materials, see CONFLICTS.md sec7 and BUILD_READINESS.md sec2). Confirm this purchase is intentional (reserve stock / RQ2 baseline archive) rather than assumed as a current flight-part material.</t>
+          <t>DROPPED 2026-08-14 at program direction. ABS is removed from RQ2 entirely: the zoned-materials study is now ASA-Aero / PETG-CF / PC-FR against plain PC, and the blast-shield screen drops from six materials to five (PLA, PETG-CF, ASA-Aero, PC, PC-FR). Update Build_Guide and GSE_TestStands to match.</t>
         </is>
       </c>
       <c r="F53" s="45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="46" t="n">
-        <v>16.99</v>
+        <v>0</v>
       </c>
       <c r="H53" s="46">
         <f>F53*G53</f>
@@ -2153,14 +2159,14 @@
       </c>
       <c r="E54" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09b: real Amazon cart item (swapped from Bambu Lab sourcing). WARNING - this material was struck from the design scope in 2026-08b (PC-FR/ASA-Aero/ABS/PC coupon-testing program dropped; PLA+PETG-CF are the only current airframe materials, see CONFLICTS.md sec7 and BUILD_READINESS.md sec2). Confirm this purchase is intentional (reserve stock / RQ2 baseline archive) rather than assumed as a current flight-part material.</t>
+          <t>2026-08-13: in cart at $31.99 (was $28.79). RQ2 comparison material (plain PC vs PC-FR) and blast-shield screen coupon.</t>
         </is>
       </c>
       <c r="F54" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="46" t="n">
-        <v>28.79</v>
+        <v>31.99</v>
       </c>
       <c r="H54" s="46">
         <f>F54*G54</f>
@@ -2190,14 +2196,14 @@
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09c: real Amazon cart item, added. Plain ASA (Black), not the same as the Bambu ASA-Aero (White, row 52, foamed/lightweight variant) already in the BOM - both now present. Same scope-mismatch flag as the rest of Section 6: not the design's current PLA+PETG-CF material, confirm intentional.</t>
+          <t>2026-08-13: in cart at $16.19 (was $17.99), limited-time deal. Plain ASA (Black) - NOT the same as Bambu ASA-Aero (row 52), which is the foamed low-density grade the mass cascade assumes. Use for fixtures and the RQ2 screen, not the airframe.</t>
         </is>
       </c>
       <c r="F55" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="46" t="n">
-        <v>17.99</v>
+        <v>16.19</v>
       </c>
       <c r="H55" s="46">
         <f>F55*G55</f>
@@ -2205,156 +2211,161 @@
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="34">
-      <c r="A56" s="47" t="inlineStr">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>ELEGOO Rapid PETG (Black), Amazon - 1 kg</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>B0CPF7FDTG</t>
+        </is>
+      </c>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E56" s="44" t="inlineStr">
+        <is>
+          <t>2026-08-13: NEW cart line. Plain PETG, NOT the PETG-CF that the lower body tube and fins are specified in (PETG-CF is in Already Acquired, 2 kg). Use for prototyping, jigs, fixtures and the RQ2 blast-shield screen - not flight structure.</t>
+        </is>
+      </c>
+      <c r="F56" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="46" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="H56" s="46">
+        <f>F56*G56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>ELEGOO PLA-CF (Black), Amazon - 1 kg</t>
+        </is>
+      </c>
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>B0D86M3RM4</t>
+        </is>
+      </c>
+      <c r="D57" s="43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E57" s="44" t="inlineStr">
+        <is>
+          <t>2026-08-13: NEW cart line. PLA-CF is NOT a flown material - the zoning is ASA-Aero / PETG-CF / PC-FR. Fine for tooling and as a sixth blast-shield screen coupon, but keep it out of the airframe: PLA HDT ~55 C is below the predicted engine-bay wall temperature.</t>
+        </is>
+      </c>
+      <c r="F57" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="46" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="H57" s="46">
+        <f>F57*G57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="34">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="48" t="n"/>
-      <c r="D56" s="48" t="n"/>
-      <c r="E56" s="48" t="n"/>
-      <c r="F56" s="48" t="n"/>
-      <c r="G56" s="48" t="n"/>
-      <c r="H56" s="49">
-        <f>SUM(H51:H55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="34">
-      <c r="A58" s="37" t="inlineStr">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="48" t="n"/>
+      <c r="D58" s="48" t="n"/>
+      <c r="E58" s="48" t="n"/>
+      <c r="F58" s="48" t="n"/>
+      <c r="G58" s="48" t="n"/>
+      <c r="H58" s="49">
+        <f>SUM(H51:H57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="34"/>
+    <row r="60" ht="15" customHeight="1" s="34">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>7. Harness, connectors, prototyping &amp; assembly</t>
         </is>
       </c>
-      <c r="B58" s="38" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="38" t="n"/>
-      <c r="H58" s="38" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="34">
-      <c r="A59" s="39" t="inlineStr">
+      <c r="B60" s="38" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/gp/product/B07QZYC5PG</t>
+        </is>
+      </c>
+      <c r="E60" s="38" t="n"/>
+      <c r="F60" s="38" t="n"/>
+      <c r="G60" s="38" t="n"/>
+      <c r="H60" s="38" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="34">
+      <c r="A61" s="39" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="B61" s="39" t="inlineStr">
         <is>
           <t>Storefront</t>
         </is>
       </c>
-      <c r="C59" s="39" t="inlineStr">
+      <c r="C61" s="39" t="inlineStr">
         <is>
           <t>Part # / Spec</t>
         </is>
       </c>
-      <c r="D59" s="39" t="inlineStr">
+      <c r="D61" s="39" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="E59" s="39" t="inlineStr">
+      <c r="E61" s="39" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F59" s="40" t="inlineStr">
+      <c r="F61" s="40" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G59" s="40" t="inlineStr">
+      <c r="G61" s="40" t="inlineStr">
         <is>
           <t>Unit ($)</t>
         </is>
       </c>
-      <c r="H59" s="40" t="inlineStr">
+      <c r="H61" s="40" t="inlineStr">
         <is>
           <t>Line ($)</t>
         </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="34">
-      <c r="A60" s="41" t="inlineStr">
-        <is>
-          <t>ZSHX lead-free solder Sn99/Ag0.3/Cu0.7 (0.8 mm, 100 g)</t>
-        </is>
-      </c>
-      <c r="B60" s="42" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="C60" s="42" t="inlineStr">
-        <is>
-          <t>B07QZYC5PG</t>
-        </is>
-      </c>
-      <c r="D60" s="43" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E60" s="44" t="inlineStr">
-        <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
-        </is>
-      </c>
-      <c r="F60" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="46">
-        <f>F60*G60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="34">
-      <c r="A61" s="41" t="inlineStr">
-        <is>
-          <t>TUOFENG 24 AWG flexible silicone wire kit (6-color, 30 ft)</t>
-        </is>
-      </c>
-      <c r="B61" s="42" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="C61" s="42" t="inlineStr">
-        <is>
-          <t>B07G2BWBX8</t>
-        </is>
-      </c>
-      <c r="D61" s="43" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E61" s="44" t="inlineStr">
-        <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
-        </is>
-      </c>
-      <c r="F61" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="46">
-        <f>F61*G61</f>
-        <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="34">
       <c r="A62" s="41" t="inlineStr">
         <is>
-          <t>HANGLIFE heat-set insert assortment M2-M6 (345 pc)</t>
+          <t>ZSHX lead-free solder Sn99/Ag0.3/Cu0.7 (0.8 mm, 100 g)</t>
         </is>
       </c>
       <c r="B62" s="42" t="inlineStr">
@@ -2364,7 +2375,7 @@
       </c>
       <c r="C62" s="42" t="inlineStr">
         <is>
-          <t>B0CS6WXQPM</t>
+          <t>B07QZYC5PG</t>
         </is>
       </c>
       <c r="D62" s="43" t="inlineStr">
@@ -2374,14 +2385,14 @@
       </c>
       <c r="E62" s="44" t="inlineStr">
         <is>
-          <t>2026-08-09f: confirmed in cart ($19.99). Un-zeroed from earlier NOT IN CURRENT CART flag.</t>
+          <t>NOT IN EITHER CART (2026-08-14). Lead-free solder for the perfboard build. Still open.</t>
         </is>
       </c>
       <c r="F62" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="46" t="n">
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="H62" s="46">
         <f>F62*G62</f>
@@ -2391,17 +2402,17 @@
     <row r="63" ht="15" customHeight="1" s="34">
       <c r="A63" s="41" t="inlineStr">
         <is>
-          <t>Perfboard 20x24 (50x70 mm) double-sided</t>
+          <t>24 AWG flexible silicone wire, 6-color (ON HAND)</t>
         </is>
       </c>
       <c r="B63" s="42" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C63" s="42" t="inlineStr">
         <is>
-          <t>PID 1609</t>
+          <t>B07G2BWBX8</t>
         </is>
       </c>
       <c r="D63" s="43" t="inlineStr">
@@ -2411,11 +2422,11 @@
       </c>
       <c r="E63" s="44" t="inlineStr">
         <is>
-          <t>Flight computer card. Mounts on edge in 02b_fc_card_carrier_{fwd,aft}. Generic Elegoo-type board.</t>
+          <t>ALREADY ACQUIRED 2026-08-14.</t>
         </is>
       </c>
       <c r="F63" s="45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G63" s="46" t="n">
         <v>0</v>
@@ -2428,17 +2439,17 @@
     <row r="64" ht="15" customHeight="1" s="34">
       <c r="A64" s="41" t="inlineStr">
         <is>
-          <t>Multi-colored heat-shrink pack</t>
+          <t>HANGLIFE heat-set insert assortment M2-M6 (345 pc)</t>
         </is>
       </c>
       <c r="B64" s="42" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C64" s="42" t="inlineStr">
         <is>
-          <t>PID 1649</t>
+          <t>B0CS6WXQPM</t>
         </is>
       </c>
       <c r="D64" s="43" t="inlineStr">
@@ -2448,14 +2459,14 @@
       </c>
       <c r="E64" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>2026-08-13: in cart at $19.99. M2-M6 assortment covers the gimbal, FC card carriers, bulkhead and both ground stands.</t>
         </is>
       </c>
       <c r="F64" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="46" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="H64" s="46">
         <f>F64*G64</f>
@@ -2465,7 +2476,7 @@
     <row r="65" ht="15" customHeight="1" s="34">
       <c r="A65" s="41" t="inlineStr">
         <is>
-          <t>High-temp polyimide tape 1 cm x 33 m</t>
+          <t>Perfboard 20x24 (50x70 mm) double-sided</t>
         </is>
       </c>
       <c r="B65" s="42" t="inlineStr">
@@ -2475,7 +2486,7 @@
       </c>
       <c r="C65" s="42" t="inlineStr">
         <is>
-          <t>PID 3057</t>
+          <t>PID 1609</t>
         </is>
       </c>
       <c r="D65" s="43" t="inlineStr">
@@ -2485,11 +2496,11 @@
       </c>
       <c r="E65" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>*** NOT IN THE ADAFRUIT CART (2026-08-14) - zeroed but REQUIRED. *** Flight computer card, 20x24 holes (50x70 mm), mounts on edge in 02b_fc_card_carrier_{fwd,aft}. Need two (flight + ground stand). Generic equivalent fine, but the hole count must be 20x24 or the wiring diagram stops matching.</t>
         </is>
       </c>
       <c r="F65" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G65" s="46" t="n">
         <v>0</v>
@@ -2502,7 +2513,7 @@
     <row r="66" ht="15" customHeight="1" s="34">
       <c r="A66" s="41" t="inlineStr">
         <is>
-          <t>Adafruit male header 36-pin short breakaway (10-pk)</t>
+          <t>Multi-colored heat-shrink pack (ON HAND)</t>
         </is>
       </c>
       <c r="B66" s="42" t="inlineStr">
@@ -2512,7 +2523,7 @@
       </c>
       <c r="C66" s="42" t="inlineStr">
         <is>
-          <t>PID 3009</t>
+          <t>PID 1649</t>
         </is>
       </c>
       <c r="D66" s="43" t="inlineStr">
@@ -2522,11 +2533,11 @@
       </c>
       <c r="E66" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>ALREADY ACQUIRED 2026-08-14.</t>
         </is>
       </c>
       <c r="F66" s="45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="46" t="n">
         <v>0</v>
@@ -2539,7 +2550,7 @@
     <row r="67" ht="15" customHeight="1" s="34">
       <c r="A67" s="41" t="inlineStr">
         <is>
-          <t>STEMMA QT JST-SH 4-pin to male header, 150 mm x4</t>
+          <t>High-temp polyimide (Kapton) tape (ON HAND)</t>
         </is>
       </c>
       <c r="B67" s="42" t="inlineStr">
@@ -2549,7 +2560,7 @@
       </c>
       <c r="C67" s="42" t="inlineStr">
         <is>
-          <t>PID 4209</t>
+          <t>PID 3057</t>
         </is>
       </c>
       <c r="D67" s="43" t="inlineStr">
@@ -2559,11 +2570,11 @@
       </c>
       <c r="E67" s="44" t="inlineStr">
         <is>
-          <t>One per sensor. Four male pins land in one perfboard row across the GND/SDA/SCL/3V3 buses.</t>
+          <t>ALREADY ACQUIRED 2026-08-14.</t>
         </is>
       </c>
       <c r="F67" s="45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G67" s="46" t="n">
         <v>0</v>
@@ -2576,7 +2587,7 @@
     <row r="68" ht="15" customHeight="1" s="34">
       <c r="A68" s="41" t="inlineStr">
         <is>
-          <t>Dupont M-F extension leads (separation joint)</t>
+          <t>Male header, 36-pin breakaway (ON HAND)</t>
         </is>
       </c>
       <c r="B68" s="42" t="inlineStr">
@@ -2586,7 +2597,7 @@
       </c>
       <c r="C68" s="42" t="inlineStr">
         <is>
-          <t>PID 757</t>
+          <t>PID 3009</t>
         </is>
       </c>
       <c r="D68" s="43" t="inlineStr">
@@ -2596,11 +2607,11 @@
       </c>
       <c r="E68" s="44" t="inlineStr">
         <is>
-          <t>Seven leads cross the bulkhead and part at ejection: 2x servo sig, +5V, GND, SDA, SCL, 3V3.</t>
+          <t>ALREADY ACQUIRED 2026-08-14.</t>
         </is>
       </c>
       <c r="F68" s="45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" s="46" t="n">
         <v>0</v>
@@ -2613,7 +2624,7 @@
     <row r="69" ht="15" customHeight="1" s="34">
       <c r="A69" s="41" t="inlineStr">
         <is>
-          <t>2.54 mm terminal block, 2-pin</t>
+          <t>STEMMA QT JST-SH 4-pin to premium male header, 150 mm</t>
         </is>
       </c>
       <c r="B69" s="42" t="inlineStr">
@@ -2623,7 +2634,7 @@
       </c>
       <c r="C69" s="42" t="inlineStr">
         <is>
-          <t>PID 2138</t>
+          <t>PID 4209</t>
         </is>
       </c>
       <c r="D69" s="43" t="inlineStr">
@@ -2633,14 +2644,14 @@
       </c>
       <c r="E69" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>2026-08-14: qty6 in the Adafruit cart. Four sensors need four; two spare. The four male pins land in one perfboard row across the GND/SDA/SCL/3V3 bus rails.</t>
         </is>
       </c>
       <c r="F69" s="45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G69" s="46" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H69" s="46">
         <f>F69*G69</f>
@@ -2650,7 +2661,7 @@
     <row r="70" ht="15" customHeight="1" s="34">
       <c r="A70" s="41" t="inlineStr">
         <is>
-          <t>USB-C to Micro-B cable, 3 ft</t>
+          <t>Premium F/M extension jumper wires, 40 x 150 mm</t>
         </is>
       </c>
       <c r="B70" s="42" t="inlineStr">
@@ -2660,7 +2671,7 @@
       </c>
       <c r="C70" s="42" t="inlineStr">
         <is>
-          <t>PID 3878</t>
+          <t>PID 826</t>
         </is>
       </c>
       <c r="D70" s="43" t="inlineStr">
@@ -2670,14 +2681,14 @@
       </c>
       <c r="E70" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>2026-08-14: REPLACES the PID 757 dupont pack. Forty leads covers the seven that cross the bulkhead and part at ejection (SERVO1_SIG, SERVO2_SIG, +5V, GND, SDA, SCL, 3V3) with heavy margin. *** REACH CHECK: the gimbal BNO085 run is roughly 313 mm from the FC card at station 235 mm to the pivot at 548 mm, plus routing slack. A 150 mm PID 4209 plus one 150 mm extension is 300 mm and comes up short - chain TWO extensions (450 mm) for that run. This is why the 400 mm STEMMA QT (row 107) is no longer needed. ***</t>
         </is>
       </c>
       <c r="F70" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="46" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="H70" s="46">
         <f>F70*G70</f>
@@ -2687,7 +2698,7 @@
     <row r="71" ht="15" customHeight="1" s="34">
       <c r="A71" s="41" t="inlineStr">
         <is>
-          <t>Silicone USB-C dust cover inserts (10-pk)</t>
+          <t>2.54 mm terminal block, 2-pin</t>
         </is>
       </c>
       <c r="B71" s="42" t="inlineStr">
@@ -2697,7 +2708,7 @@
       </c>
       <c r="C71" s="42" t="inlineStr">
         <is>
-          <t>PID 4993</t>
+          <t>PID 2138</t>
         </is>
       </c>
       <c r="D71" s="43" t="inlineStr">
@@ -2707,14 +2718,14 @@
       </c>
       <c r="E71" s="44" t="inlineStr">
         <is>
-          <t>in Adafruit cart (qty1) - confirmed sufficient, no more needed (2026-08-09)</t>
+          <t>2026-08-14: qty5 in cart, which is exactly right. Two per flight-computer card - pack input and UBEC 5 V output - across two cards (flight + ground stand) is four, plus one spare. The arming switch stays soldered and heat-shrunk into the pack harness rather than blocked, since it carries full pack current.</t>
         </is>
       </c>
       <c r="F71" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G71" s="46" t="n">
-        <v>1.5</v>
+        <v>0.95</v>
       </c>
       <c r="H71" s="46">
         <f>F71*G71</f>
@@ -2724,7 +2735,7 @@
     <row r="72" ht="15" customHeight="1" s="34">
       <c r="A72" s="41" t="inlineStr">
         <is>
-          <t>PCB coaster (free w/ Adafruit order)</t>
+          <t>USB-C to Micro-B cable, 3 ft</t>
         </is>
       </c>
       <c r="B72" s="42" t="inlineStr">
@@ -2734,7 +2745,7 @@
       </c>
       <c r="C72" s="42" t="inlineStr">
         <is>
-          <t>PID 5719</t>
+          <t>PID 3878</t>
         </is>
       </c>
       <c r="D72" s="43" t="inlineStr">
@@ -2744,14 +2755,14 @@
       </c>
       <c r="E72" s="44" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>2026-08-14: qty1 in cart. Programming and log-pull cable for the Pico 2 W.</t>
         </is>
       </c>
       <c r="F72" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H72" s="46">
         <f>F72*G72</f>
@@ -2759,75 +2770,75 @@
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="34">
-      <c r="A73" s="33" t="inlineStr">
-        <is>
-          <t>microSD SPI breakout board (SPI0 GP2-5; Pico has no SD slot)</t>
-        </is>
-      </c>
-      <c r="B73" s="33" t="inlineStr">
+      <c r="A73" s="41" t="inlineStr">
+        <is>
+          <t>Silicone USB-C dust cover inserts (10-pk)</t>
+        </is>
+      </c>
+      <c r="B73" s="42" t="inlineStr">
         <is>
           <t>Adafruit</t>
         </is>
       </c>
-      <c r="C73" s="33" t="inlineStr">
-        <is>
-          <t>PID 254</t>
-        </is>
-      </c>
-      <c r="D73" s="33" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E73" s="33" t="inlineStr">
-        <is>
-          <t>microSD on SPI1: MISO GP8, CS GP9, SCK GP10, MOSI GP11. Matches sd_logger.h.</t>
-        </is>
-      </c>
-      <c r="F73" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="33" t="n">
+      <c r="C73" s="42" t="inlineStr">
+        <is>
+          <t>PID 4993</t>
+        </is>
+      </c>
+      <c r="D73" s="43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E73" s="44" t="inlineStr">
+        <is>
+          <t>2026-08-13: in the Adafruit cart, qty1. Sufficient.</t>
+        </is>
+      </c>
+      <c r="F73" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H73" s="46">
+        <f>F73*G73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="34">
+      <c r="A74" s="41" t="inlineStr">
+        <is>
+          <t>PCB coaster (free w/ Adafruit order)</t>
+        </is>
+      </c>
+      <c r="B74" s="42" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>PID 5719</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E74" s="44" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F74" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="33">
-        <f>F73*G73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="34">
-      <c r="A74" s="33" t="inlineStr">
-        <is>
-          <t>1010 launch rail + pad (rail-exit gate is 1.0 m of rail)</t>
-        </is>
-      </c>
-      <c r="B74" s="33" t="inlineStr">
-        <is>
-          <t>Estes/Amazon</t>
-        </is>
-      </c>
-      <c r="C74" s="33" t="inlineStr">
-        <is>
-          <t>1010 rail</t>
-        </is>
-      </c>
-      <c r="D74" s="33" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E74" s="33" t="inlineStr">
-        <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
-        </is>
-      </c>
-      <c r="F74" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="33">
+      <c r="H74" s="46">
         <f>F74*G74</f>
         <v/>
       </c>
@@ -2835,17 +2846,17 @@
     <row r="75" ht="15" customHeight="1" s="34">
       <c r="A75" s="33" t="inlineStr">
         <is>
-          <t>Nomex chute protector blanket (ejection-gas shield)</t>
+          <t>microSD SPI breakout (ON HAND - see Already Acquired)</t>
         </is>
       </c>
       <c r="B75" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>12x12 in Nomex</t>
+          <t>PID 254</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
@@ -2855,11 +2866,11 @@
       </c>
       <c r="E75" s="33" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>ALREADY ACQUIRED 2026-08-13 - moved to the Already Acquired sheet, zeroed here to avoid double-counting. microSD on SPI1: MISO GP8, CS GP9, SCK GP10, MOSI GP11. Matches sd_logger.h.</t>
         </is>
       </c>
       <c r="F75" s="33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="33" t="n">
         <v>0</v>
@@ -2872,17 +2883,17 @@
     <row r="76" ht="15" customHeight="1" s="34">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>Handheld anemometer (launch-site wind; RQ3 margin + go/no-go)</t>
+          <t>1010 launch rail + pad (ON HAND)</t>
         </is>
       </c>
       <c r="B76" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Estes/Amazon</t>
         </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>vane anemometer</t>
+          <t>1010 rail</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
@@ -2892,11 +2903,11 @@
       </c>
       <c r="E76" s="33" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>ALREADY ACQUIRED 2026-08-14. Rail-exit gate is 1.0 m of rail.</t>
         </is>
       </c>
       <c r="F76" s="33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="33" t="n">
         <v>0</v>
@@ -2909,17 +2920,17 @@
     <row r="77" ht="15" customHeight="1" s="34">
       <c r="A77" s="33" t="inlineStr">
         <is>
-          <t>Steel blast deflector plate (static stand; PC-FR will not survive)</t>
+          <t>Nomex chute protector blanket (ON HAND)</t>
         </is>
       </c>
       <c r="B77" s="33" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>mild steel ~150 mm sq</t>
+          <t>12x12 in Nomex</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
@@ -2929,11 +2940,11 @@
       </c>
       <c r="E77" s="33" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>ALREADY ACQUIRED 2026-08-14.</t>
         </is>
       </c>
       <c r="F77" s="33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="33" t="n">
         <v>0</v>
@@ -2946,17 +2957,17 @@
     <row r="78" ht="15" customHeight="1" s="34">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>BMP388 barometric sensor (FLIGHT-BLOCKING - not in cart)</t>
+          <t>Handheld anemometer (launch-site wind; RQ3 margin + go/no-go)</t>
         </is>
       </c>
       <c r="B78" s="33" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>PID 3966</t>
+          <t>vane anemometer</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
@@ -2966,11 +2977,11 @@
       </c>
       <c r="E78" s="33" t="inlineStr">
         <is>
-          <t>DUPLICATE of row 8 (BMP388) - zeroed to avoid double-counting. Not in current carts.</t>
+          <t>NOT IN EITHER CART (2026-08-14). Launch-site wind for the go/no-go gate. Confirm whether one is on hand.</t>
         </is>
       </c>
       <c r="F78" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="33" t="n">
         <v>0</v>
@@ -2983,17 +2994,17 @@
     <row r="79" ht="15" customHeight="1" s="34">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>Decoupling kit: 1000 uF + 100 uF low-ESR + SS34 Schottky</t>
+          <t>Steel blast deflector plate (static stand; PC-FR will not survive)</t>
         </is>
       </c>
       <c r="B79" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>low-ESR + SS34</t>
+          <t>mild steel ~150 mm sq</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
@@ -3003,7 +3014,7 @@
       </c>
       <c r="E79" s="33" t="inlineStr">
         <is>
-          <t>DUPLICATE of row 18 (decoupling kit) - zeroed to avoid double-counting.</t>
+          <t>NOT IN EITHER CART (2026-08-14). Static-stand blast deflector - PC-FR will not survive the plume. Confirm whether one is on hand or can be sourced locally.</t>
         </is>
       </c>
       <c r="F79" s="33" t="n">
@@ -3020,17 +3031,17 @@
     <row r="80" ht="15" customHeight="1" s="34">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>SPDT slide arming switch (RBF sense on GP22)</t>
+          <t>BMP388 barometric sensor (FLIGHT-BLOCKING - not in cart)</t>
         </is>
       </c>
       <c r="B80" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>SPDT slide</t>
+          <t>PID 3966</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
@@ -3040,7 +3051,7 @@
       </c>
       <c r="E80" s="33" t="inlineStr">
         <is>
-          <t>DUPLICATE of row 20 (arming switch) - zeroed to avoid double-counting.</t>
+          <t>DUPLICATE of row 8 (BMP388) - zeroed to avoid double-counting. Not in current carts.</t>
         </is>
       </c>
       <c r="F80" s="33" t="n">
@@ -3057,7 +3068,7 @@
     <row r="81" ht="15" customHeight="1" s="34">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>LiPo balance charger (2S)</t>
+          <t>Decoupling kit: 1000 uF + 100 uF low-ESR + SS34 Schottky</t>
         </is>
       </c>
       <c r="B81" s="33" t="inlineStr">
@@ -3067,7 +3078,7 @@
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>HTRC B3</t>
+          <t>low-ESR + SS34</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
@@ -3077,7 +3088,7 @@
       </c>
       <c r="E81" s="33" t="inlineStr">
         <is>
-          <t>DUPLICATE of row 17 (LiPo charger, now SSUPCHG in cart) - zeroed to avoid double-counting.</t>
+          <t>DUPLICATE of row 18 (decoupling kit) - zeroed to avoid double-counting.</t>
         </is>
       </c>
       <c r="F81" s="33" t="n">
@@ -3094,17 +3105,17 @@
     <row r="82" ht="15" customHeight="1" s="34">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>Calibration masses to ~2.5 kg (Gate 4 load-cell cal)</t>
+          <t>SPDT slide arming switch (RBF sense on GP22)</t>
         </is>
       </c>
       <c r="B82" s="33" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>known masses</t>
+          <t>SPDT slide</t>
         </is>
       </c>
       <c r="D82" s="33" t="inlineStr">
@@ -3114,11 +3125,11 @@
       </c>
       <c r="E82" s="33" t="inlineStr">
         <is>
-          <t>DUPLICATE of row 93 (UCEC calibration weights, actual cart item) - zeroed to avoid double-counting.</t>
+          <t>DUPLICATE of row 20 (arming switch) - zeroed to avoid double-counting.</t>
         </is>
       </c>
       <c r="F82" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" s="33" t="n">
         <v>0</v>
@@ -3131,7 +3142,7 @@
     <row r="83" ht="15" customHeight="1" s="34">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>M2 ball-link rod ends, 10-pk (RE-SOURCED - original ships Aug 12-21)</t>
+          <t>LiPo balance charger (2S)</t>
         </is>
       </c>
       <c r="B83" s="33" t="inlineStr">
@@ -3141,7 +3152,7 @@
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>B0F1XK7H11</t>
+          <t>HTRC B3</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
@@ -3151,7 +3162,7 @@
       </c>
       <c r="E83" s="33" t="inlineStr">
         <is>
-          <t>DUPLICATE of row 27 (rod-end ball joints, actual cart ASIN B07Q2V3R61) - zeroed to avoid double-counting.</t>
+          <t>DUPLICATE of row 17 (LiPo charger, now SSUPCHG in cart) - zeroed to avoid double-counting.</t>
         </is>
       </c>
       <c r="F83" s="33" t="n">
@@ -3166,181 +3177,181 @@
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="34">
-      <c r="A84" s="47" t="inlineStr">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>Calibration masses to ~2.5 kg (Gate 4 load-cell cal)</t>
+        </is>
+      </c>
+      <c r="B84" s="33" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>known masses</t>
+        </is>
+      </c>
+      <c r="D84" s="33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E84" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE of row 93 (UCEC calibration weights, actual cart item) - zeroed to avoid double-counting.</t>
+        </is>
+      </c>
+      <c r="F84" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="33">
+        <f>F84*G84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="34">
+      <c r="A85" s="33" t="inlineStr">
+        <is>
+          <t>M2 ball-link rod ends, 10-pk (RE-SOURCED - original ships Aug 12-21)</t>
+        </is>
+      </c>
+      <c r="B85" s="33" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>B0F1XK7H11</t>
+        </is>
+      </c>
+      <c r="D85" s="33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E85" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE of row 27 (rod-end ball joints, actual cart ASIN B07Q2V3R61) - zeroed to avoid double-counting.</t>
+        </is>
+      </c>
+      <c r="F85" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="33">
+        <f>F85*G85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="34">
+      <c r="A86" s="47" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B84" s="48" t="n"/>
-      <c r="C84" s="48" t="n"/>
-      <c r="D84" s="48" t="inlineStr">
+      <c r="B86" s="48" t="n"/>
+      <c r="C86" s="48" t="n"/>
+      <c r="D86" s="48" t="inlineStr">
         <is>
           <t>https://www.adafruit.com/product/4543</t>
         </is>
       </c>
-      <c r="E84" s="48" t="n"/>
-      <c r="F84" s="48" t="n"/>
-      <c r="G84" s="48" t="n"/>
-      <c r="H84" s="49">
-        <f>SUM(H60:H83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="34">
-      <c r="D85" s="33" t="inlineStr">
+      <c r="E86" s="48" t="n"/>
+      <c r="F86" s="48" t="n"/>
+      <c r="G86" s="48" t="n"/>
+      <c r="H86" s="49">
+        <f>SUM(H62:H85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="34">
+      <c r="D87" s="33" t="inlineStr">
         <is>
           <t>https://www.adafruit.com/product/5974</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="34">
-      <c r="A86" s="37" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="34">
+      <c r="A88" s="37" t="inlineStr">
         <is>
           <t>8. Ground test - TVC balance + static stand (load cells + DAQ)</t>
         </is>
       </c>
-      <c r="B86" s="38" t="n"/>
-      <c r="C86" s="38" t="n"/>
-      <c r="D86" s="38" t="inlineStr">
+      <c r="B88" s="38" t="n"/>
+      <c r="C88" s="38" t="n"/>
+      <c r="D88" s="38" t="inlineStr">
         <is>
           <t>https://www.adafruit.com/product/5302</t>
         </is>
       </c>
-      <c r="E86" s="38" t="n"/>
-      <c r="F86" s="38" t="n"/>
-      <c r="G86" s="38" t="n"/>
-      <c r="H86" s="38" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="34">
-      <c r="A87" s="39" t="inlineStr">
+      <c r="E88" s="38" t="n"/>
+      <c r="F88" s="38" t="n"/>
+      <c r="G88" s="38" t="n"/>
+      <c r="H88" s="38" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="34">
+      <c r="A89" s="39" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B87" s="39" t="inlineStr">
+      <c r="B89" s="39" t="inlineStr">
         <is>
           <t>Storefront</t>
         </is>
       </c>
-      <c r="C87" s="39" t="inlineStr">
+      <c r="C89" s="39" t="inlineStr">
         <is>
           <t>Part # / Spec</t>
         </is>
       </c>
-      <c r="D87" s="39" t="inlineStr">
+      <c r="D89" s="39" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="E87" s="39" t="inlineStr">
+      <c r="E89" s="39" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F87" s="40" t="inlineStr">
+      <c r="F89" s="40" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G87" s="40" t="inlineStr">
+      <c r="G89" s="40" t="inlineStr">
         <is>
           <t>Unit ($)</t>
         </is>
       </c>
-      <c r="H87" s="40" t="inlineStr">
+      <c r="H89" s="40" t="inlineStr">
         <is>
           <t>Line ($)</t>
         </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="34">
-      <c r="A88" s="41" t="inlineStr">
-        <is>
-          <t>Adafruit strain-gauge load cell 1 kg (lateral X,Y)</t>
-        </is>
-      </c>
-      <c r="B88" s="42" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="C88" s="42" t="inlineStr">
-        <is>
-          <t>PID 4540</t>
-        </is>
-      </c>
-      <c r="D88" s="43" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E88" s="44" t="inlineStr">
-        <is>
-          <t>in Adafruit cart</t>
-        </is>
-      </c>
-      <c r="F88" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G88" s="46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H88" s="46">
-        <f>F88*G88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="34">
-      <c r="A89" s="41" t="inlineStr">
-        <is>
-          <t>Adafruit strain-gauge load cell 20 kg (static stand)</t>
-        </is>
-      </c>
-      <c r="B89" s="42" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="C89" s="42" t="inlineStr">
-        <is>
-          <t>PID 4543</t>
-        </is>
-      </c>
-      <c r="D89" s="43" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E89" s="44" t="inlineStr">
-        <is>
-          <t>in Adafruit cart</t>
-        </is>
-      </c>
-      <c r="F89" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" s="46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H89" s="46">
-        <f>F89*G89</f>
-        <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="34">
       <c r="A90" s="41" t="inlineStr">
         <is>
-          <t>Adafruit HX711 24-bit ADC</t>
+          <t>Adafruit strain-gauge load cell 1 kg (lateral X,Y)</t>
         </is>
       </c>
       <c r="B90" s="42" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C90" s="42" t="inlineStr">
         <is>
-          <t>HiLetgo B00XRRNCOO (3pcs pack)</t>
+          <t>PID 4540</t>
         </is>
       </c>
       <c r="D90" s="43" t="inlineStr">
@@ -3350,14 +3361,14 @@
       </c>
       <c r="E90" s="44" t="inlineStr">
         <is>
-          <t>Cart reconciliation 2026-08-09e: cart has qty3 (3x 3-pack = 9 units), not 2 - increased from qty2 to match live cart.</t>
+          <t>SIZING CONFIRMED 2026-08-13: LATERAL X and Y on the TVC balance. Side force at the nozzle is T*sin(8 deg) = 25.3*0.139 = 3.5 N = 0.36 kgf, so a 1 kg (9.8 N) cell sits at 36 percent of full scale - inside Adafruit's own 2x rule with room for a hard-over. qty2 = one per lateral axis.</t>
         </is>
       </c>
       <c r="F90" s="45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="46" t="n">
-        <v>6.79</v>
+        <v>3.95</v>
       </c>
       <c r="H90" s="46">
         <f>F90*G90</f>
@@ -3367,17 +3378,17 @@
     <row r="91" ht="15" customHeight="1" s="34">
       <c r="A91" s="41" t="inlineStr">
         <is>
-          <t>Adafruit KB2040 (RP2040) - spare/bench DAQ</t>
+          <t>RQ2 bend-to-fracture rig (printed supports + hanger yoke)</t>
         </is>
       </c>
       <c r="B91" s="42" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>In-house</t>
         </is>
       </c>
       <c r="C91" s="42" t="inlineStr">
         <is>
-          <t>PID 5302</t>
+          <t>PETG-CF (printed)</t>
         </is>
       </c>
       <c r="D91" s="43" t="inlineStr">
@@ -3387,7 +3398,7 @@
       </c>
       <c r="E91" s="44" t="inlineStr">
         <is>
-          <t>NOT IN CURRENT CART (2026-08-09) - zeroed from to-buy total; still needed, purchase separately</t>
+          <t>REINSTATED 2026-08-14 in a new form. No load cell: coupons are loaded by hanging dead weight until fracture, so the force reference is gravity rather than a calibrated bridge. Rig is two printed support blocks carrying 6 mm rollers at an 80 mm span plus a mid-span hanger yoke. Design ceiling 6 kg (59 N); predicted fracture is 1.4 to 4.8 kgf depending on material. Weight comes from known masses, not a purchase. The 20 kg load cell that used to carry this line is not needed and stays dropped.</t>
         </is>
       </c>
       <c r="F91" s="45" t="n">
@@ -3404,17 +3415,17 @@
     <row r="92" ht="15" customHeight="1" s="34">
       <c r="A92" s="41" t="inlineStr">
         <is>
-          <t>Digital load cell + HX711, 5 kg (2 sets) - axial Z</t>
+          <t>Adafruit HX711 24-bit ADC (load-cell front end)</t>
         </is>
       </c>
       <c r="B92" s="42" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C92" s="42" t="inlineStr">
         <is>
-          <t>B09K7G3477</t>
+          <t>PID 5974</t>
         </is>
       </c>
       <c r="D92" s="43" t="inlineStr">
@@ -3424,14 +3435,14 @@
       </c>
       <c r="E92" s="44" t="inlineStr">
         <is>
-          <t>DROPPED 2026-08-09 - replaced by Adafruit 5kg cell (Section 9, row 106). Zeroed to avoid double-counting.</t>
+          <t>2026-08-14: qty4 in the Adafruit cart - shortfall RESOLVED. One HX711 per axis is required because the part multiplexes both channels through a single ADC and needs settling time after a channel switch, so a 3-axis balance cannot sample simultaneously off one chip. Three for the TVC balance (X, Y, Z) + one static stand. Strap RATE high for 80 SPS rather than the 10 SPS default.</t>
         </is>
       </c>
       <c r="F92" s="45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G92" s="46" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H92" s="46">
         <f>F92*G92</f>
@@ -3441,17 +3452,17 @@
     <row r="93" ht="15" customHeight="1" s="34">
       <c r="A93" s="41" t="inlineStr">
         <is>
-          <t>UCEC calibration weight set 10 mg-100 g</t>
+          <t>Adafruit KB2040 (RP2040) - spare/bench DAQ</t>
         </is>
       </c>
       <c r="B93" s="42" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C93" s="42" t="inlineStr">
         <is>
-          <t>B08R8RGCRS</t>
+          <t>PID 5302</t>
         </is>
       </c>
       <c r="D93" s="43" t="inlineStr">
@@ -3461,14 +3472,14 @@
       </c>
       <c r="E93" s="44" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>2026-08-13: IN THE ADAFRUIT CART AS A FREEBIE ($0). Spare/bench DAQ, not flight hardware.</t>
         </is>
       </c>
       <c r="F93" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G93" s="46" t="n">
-        <v>9.99</v>
+        <v>0</v>
       </c>
       <c r="H93" s="46">
         <f>F93*G93</f>
@@ -3476,55 +3487,101 @@
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="34">
-      <c r="A94" s="47" t="inlineStr">
+      <c r="A94" s="41" t="inlineStr">
+        <is>
+          <t>Digital load cell + HX711, 5 kg (2 sets) - axial Z</t>
+        </is>
+      </c>
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>B09K7G3477</t>
+        </is>
+      </c>
+      <c r="D94" s="43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E94" s="44" t="inlineStr">
+        <is>
+          <t>DROPPED 2026-08-09 - replaced by Adafruit 5kg cell (Section 9, row 106). Zeroed to avoid double-counting.</t>
+        </is>
+      </c>
+      <c r="F94" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="46">
+        <f>F94*G94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="34">
+      <c r="A95" s="41" t="inlineStr">
+        <is>
+          <t>UCEC calibration weight set 10 mg-100 g</t>
+        </is>
+      </c>
+      <c r="B95" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C95" s="42" t="inlineStr">
+        <is>
+          <t>B08R8RGCRS</t>
+        </is>
+      </c>
+      <c r="D95" s="43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E95" s="44" t="inlineStr">
+        <is>
+          <t>2026-08-13: in cart at $9.99. 10 mg - 100 g set calibrates every load cell before each firing. NOTE: the 20 kg bend cell and the 5 kg thrust cells want calibration points well above 100 g - add known masses up to ~2.5 kg from anything with a verified weight.</t>
+        </is>
+      </c>
+      <c r="F95" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="46" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H95" s="46">
+        <f>F95*G95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="34">
+      <c r="A96" s="47" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B94" s="48" t="n"/>
-      <c r="C94" s="48" t="n"/>
-      <c r="D94" s="48" t="n"/>
-      <c r="E94" s="48" t="n"/>
-      <c r="F94" s="48" t="n"/>
-      <c r="G94" s="48" t="n"/>
-      <c r="H94" s="49">
-        <f>SUM(H88:H93)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="34"/>
-    <row r="96" ht="15" customHeight="1" s="34">
-      <c r="A96" s="50" t="inlineStr">
+      <c r="B96" s="48" t="n"/>
+      <c r="C96" s="48" t="n"/>
+      <c r="D96" s="48" t="n"/>
+      <c r="E96" s="48" t="n"/>
+      <c r="F96" s="48" t="n"/>
+      <c r="G96" s="48" t="n"/>
+      <c r="H96" s="49">
+        <f>SUM(H90:H95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="34"/>
+    <row r="98" ht="15" customHeight="1" s="34">
+      <c r="A98" s="50" t="inlineStr">
         <is>
           <t>GROSS TO-BUY TOTAL</t>
-        </is>
-      </c>
-      <c r="B96" s="51" t="n"/>
-      <c r="C96" s="51" t="n"/>
-      <c r="D96" s="51" t="n"/>
-      <c r="E96" s="51" t="n"/>
-      <c r="F96" s="51" t="n"/>
-      <c r="G96" s="51" t="n"/>
-      <c r="H96" s="52">
-        <f>H11+H21+H29+H37+H47+H56+H84+H94+H111+H124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="34">
-      <c r="A97" s="53" t="inlineStr">
-        <is>
-          <t>Less: Estes Pro Series II Launch Controller (reimbursed)</t>
-        </is>
-      </c>
-      <c r="H97" s="54">
-        <f>-39.6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="34">
-      <c r="A98" s="55" t="inlineStr">
-        <is>
-          <t>NET OUT-OF-POCKET (still to buy)</t>
         </is>
       </c>
       <c r="B98" s="51" t="n"/>
@@ -3533,148 +3590,103 @@
       <c r="E98" s="51" t="n"/>
       <c r="F98" s="51" t="n"/>
       <c r="G98" s="51" t="n"/>
-      <c r="H98" s="56">
-        <f>H96+H97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="34"/>
+      <c r="H98" s="52">
+        <f>H11+H21+H29+H37+H47+H58+H86+H96+H113+H126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="34">
+      <c r="A99" s="53" t="inlineStr">
+        <is>
+          <t>Less: Estes Pro Series II Launch Controller (reimbursed)</t>
+        </is>
+      </c>
+      <c r="H99" s="54">
+        <f>-39.6</f>
+        <v/>
+      </c>
+    </row>
     <row r="100" ht="15" customHeight="1" s="34">
-      <c r="A100" s="33" t="inlineStr">
-        <is>
-          <t>9. 2026-08-09 Cart Reconciliation &amp; Custom PCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="34">
-      <c r="A101" s="33" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B101" s="33" t="inlineStr">
-        <is>
-          <t>Storefront</t>
-        </is>
-      </c>
-      <c r="C101" s="33" t="inlineStr">
-        <is>
-          <t>Part # / Spec</t>
-        </is>
-      </c>
-      <c r="D101" s="33" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="E101" s="33" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="F101" s="33" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="G101" s="33" t="inlineStr">
-        <is>
-          <t>Unit ($)</t>
-        </is>
-      </c>
-      <c r="H101" s="33" t="inlineStr">
-        <is>
-          <t>Line ($)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A100" s="55" t="inlineStr">
+        <is>
+          <t>NET OUT-OF-POCKET (still to buy)</t>
+        </is>
+      </c>
+      <c r="B100" s="51" t="n"/>
+      <c r="C100" s="51" t="n"/>
+      <c r="D100" s="51" t="n"/>
+      <c r="E100" s="51" t="n"/>
+      <c r="F100" s="51" t="n"/>
+      <c r="G100" s="51" t="n"/>
+      <c r="H100" s="56">
+        <f>H98+H99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="34"/>
     <row r="102" ht="15" customHeight="1" s="34">
-      <c r="A102" s="57" t="inlineStr">
-        <is>
-          <t>Custom PCB fabrication (JLCPCB) - RETIRED</t>
-        </is>
-      </c>
-      <c r="B102" s="33" t="inlineStr">
-        <is>
-          <t>JLCPCB</t>
-        </is>
-      </c>
-      <c r="C102" s="33" t="inlineStr">
-        <is>
-          <t>RP2350B flight computer board</t>
-        </is>
-      </c>
-      <c r="D102" s="33" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E102" s="33" t="inlineStr">
-        <is>
-          <t>RETIRED (Pico 2 W revision): custom PCB1 dropped on schedule grounds. Files in 'Past Iterations/PCB1 (retired)/'. Zeroed.</t>
-        </is>
-      </c>
-      <c r="F102" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="33" t="n">
-        <v>0</v>
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>9. Cart reconciliation, load-cell sizing, and retired custom PCB</t>
+        </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="34">
       <c r="A103" s="33" t="inlineStr">
         <is>
-          <t>eMagTech F-F servo extension cable 10cm (10-pk)</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B103" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Storefront</t>
         </is>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
-          <t>B0FB8QJZ33</t>
+          <t>Part # / Spec</t>
         </is>
       </c>
       <c r="D103" s="33" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="E103" s="33" t="inlineStr">
         <is>
-          <t>in cart</t>
-        </is>
-      </c>
-      <c r="F103" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="33" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="H103" s="33">
-        <f>F103*G103</f>
-        <v/>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F103" s="33" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="G103" s="33" t="inlineStr">
+        <is>
+          <t>Unit ($)</t>
+        </is>
+      </c>
+      <c r="H103" s="33" t="inlineStr">
+        <is>
+          <t>Line ($)</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="34">
-      <c r="A104" s="33" t="inlineStr">
-        <is>
-          <t>BrewJa JST 1.5mm 3-pin JR-style servo wire plug converter (4pc)</t>
+      <c r="A104" s="57" t="inlineStr">
+        <is>
+          <t>Custom PCB fabrication (JLCPCB) - RETIRED</t>
         </is>
       </c>
       <c r="B104" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>JLCPCB</t>
         </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>B0CKYWY8T9</t>
+          <t>RP2350B flight computer board</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
@@ -3684,14 +3696,14 @@
       </c>
       <c r="E104" s="33" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>RETIRED (Pico 2 W revision): custom PCB1 dropped on schedule grounds. Files in 'Past Iterations/PCB1 (retired)/'. Zeroed.</t>
         </is>
       </c>
       <c r="F104" s="33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="33" t="n">
-        <v>18.59</v>
+        <v>0</v>
       </c>
       <c r="H104" s="33">
         <f>F104*G104</f>
@@ -3701,17 +3713,17 @@
     <row r="105" ht="15" customHeight="1" s="34">
       <c r="A105" s="33" t="inlineStr">
         <is>
-          <t>Adafruit STEMMA QT 4-pin cable, 400mm</t>
+          <t>eMagTech F-F servo extension cable 10cm (10-pk)</t>
         </is>
       </c>
       <c r="B105" s="33" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>PID 5385</t>
+          <t>B0FB8QJZ33</t>
         </is>
       </c>
       <c r="D105" s="33" t="inlineStr">
@@ -3721,14 +3733,14 @@
       </c>
       <c r="E105" s="33" t="inlineStr">
         <is>
-          <t>in cart (qty2, updated 2026-08-09); FC-to-external-BNO085 run across bulkhead pass-through, see Recovery.md sec5</t>
+          <t>NOT IN THE CURRENT CART (2026-08-13) - zeroed. Superseded by the Honbay 300 mm extension leads (row 28), which cover the separation-joint runs.</t>
         </is>
       </c>
       <c r="F105" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" s="33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H105" s="33">
         <f>F105*G105</f>
@@ -3738,17 +3750,17 @@
     <row r="106" ht="15" customHeight="1" s="34">
       <c r="A106" s="33" t="inlineStr">
         <is>
-          <t>Adafruit strain-gauge load cell 5kg</t>
+          <t>BrewJa JST 1.5mm 3-pin JR-style servo wire plug converter (4pc)</t>
         </is>
       </c>
       <c r="B106" s="33" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>PID 4541</t>
+          <t>B0CKYWY8T9</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
@@ -3758,14 +3770,14 @@
       </c>
       <c r="E106" s="33" t="inlineStr">
         <is>
-          <t>in cart; confirmed sourcing (Amazon 5kg cell dropped 2026-08-09, see row 92)</t>
+          <t>NOT IN THE CURRENT CART (2026-08-13) - zeroed. The EMAX servos ship with JR-style leads already; no converter needed.</t>
         </is>
       </c>
       <c r="F106" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G106" s="33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="H106" s="33">
         <f>F106*G106</f>
@@ -3775,7 +3787,7 @@
     <row r="107" ht="15" customHeight="1" s="34">
       <c r="A107" s="33" t="inlineStr">
         <is>
-          <t>Adafruit strain-gauge load cell 10kg</t>
+          <t>Adafruit STEMMA QT 4-pin cable, 400 mm - NO LONGER NEEDED</t>
         </is>
       </c>
       <c r="B107" s="33" t="inlineStr">
@@ -3785,7 +3797,7 @@
       </c>
       <c r="C107" s="33" t="inlineStr">
         <is>
-          <t>PID 4542</t>
+          <t>PID 5385</t>
         </is>
       </c>
       <c r="D107" s="33" t="inlineStr">
@@ -3795,14 +3807,14 @@
       </c>
       <c r="E107" s="33" t="inlineStr">
         <is>
-          <t>in cart; rig mapping (TVC balance vs static stand) still to confirm</t>
+          <t>SUPERSEDED 2026-08-14: the gimbal-IMU run across the bulkhead is now PID 4209 (150 mm, male header) chained through two PID 826 F/M extensions, which also gives the pull-apart separation joint the 400 mm cable never did. Removed from the Adafruit cart.</t>
         </is>
       </c>
       <c r="F107" s="33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" s="33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="H107" s="33">
         <f>F107*G107</f>
@@ -3812,7 +3824,7 @@
     <row r="108" ht="15" customHeight="1" s="34">
       <c r="A108" s="33" t="inlineStr">
         <is>
-          <t>USB-A to USB-C Adapter</t>
+          <t>Adafruit strain-gauge load cell 5 kg (AXIAL thrust - static stand + TVC balance Z)</t>
         </is>
       </c>
       <c r="B108" s="33" t="inlineStr">
@@ -3822,7 +3834,7 @@
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>PID 4175</t>
+          <t>PID 4541</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
@@ -3832,14 +3844,14 @@
       </c>
       <c r="E108" s="33" t="inlineStr">
         <is>
-          <t>REMOVED from Adafruit cart 2026-08-09 - not being ordered. Zeroed.</t>
+          <t>SIZING CONFIRMED 2026-08-13: this is the MOTOR-FORCE cell. F15 peak thrust 25.3 N = 2.58 kgf, average 14.4 N, total impulse 49.6 N.s over 3.45 s. A 5 kg (49 N) cell puts peak at 52 percent FS. qty2 = one static stand + one TVC balance Z axis. Keep the fixture tare off the cell (frame carries the stand mass) or the margin closes; if the fixture must hang on the cell, step up to the 10 kg.</t>
         </is>
       </c>
       <c r="F108" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" s="33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="H108" s="33">
         <f>F108*G108</f>
@@ -3849,17 +3861,17 @@
     <row r="109" ht="15" customHeight="1" s="34">
       <c r="A109" s="33" t="inlineStr">
         <is>
-          <t>Route Package Protection (Estes shipping insurance)</t>
+          <t>Adafruit strain-gauge load cell 10kg</t>
         </is>
       </c>
       <c r="B109" s="33" t="inlineStr">
         <is>
-          <t>Estes</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C109" s="33" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>PID 4542</t>
         </is>
       </c>
       <c r="D109" s="33" t="inlineStr">
@@ -3869,14 +3881,14 @@
       </c>
       <c r="E109" s="33" t="inlineStr">
         <is>
-          <t>in cart</t>
+          <t>DROPPED 2026-08-13 after load-cell sizing. Nothing in the program needs 10 kg: axial thrust is covered by the 5 kg (row 108), lateral by the 1 kg (row 90), and the bend rig by the 20 kg (row 91). Zeroed. Only reinstate as the axial cell if the static-stand fixture ends up hanging its own weight on the load path.</t>
         </is>
       </c>
       <c r="F109" s="33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="33" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="H109" s="33">
         <f>F109*G109</f>
@@ -3886,17 +3898,17 @@
     <row r="110" ht="15" customHeight="1" s="34">
       <c r="A110" s="33" t="inlineStr">
         <is>
-          <t>Estes 18in Rip-Stop Nylon Parachute</t>
+          <t>USB-A to USB-C Adapter</t>
         </is>
       </c>
       <c r="B110" s="33" t="inlineStr">
         <is>
-          <t>Estes</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>18in chute</t>
+          <t>PID 4175</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
@@ -3906,14 +3918,14 @@
       </c>
       <c r="E110" s="33" t="inlineStr">
         <is>
-          <t>in cart; design/sims use 24in canopy only (Mathematics.md sec6) - confirm intended use (spare/drogue) or remove</t>
+          <t>REMOVED from Adafruit cart 2026-08-09 - not being ordered. Zeroed.</t>
         </is>
       </c>
       <c r="F110" s="33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G110" s="33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H110" s="33">
         <f>F110*G110</f>
@@ -3923,141 +3935,142 @@
     <row r="111" ht="15" customHeight="1" s="34">
       <c r="A111" s="33" t="inlineStr">
         <is>
-          <t>Subtotal</t>
-        </is>
+          <t>Route Package Protection (Estes shipping insurance)</t>
+        </is>
+      </c>
+      <c r="B111" s="33" t="inlineStr">
+        <is>
+          <t>Estes</t>
+        </is>
+      </c>
+      <c r="C111" s="33" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E111" s="33" t="inlineStr">
+        <is>
+          <t>in cart</t>
+        </is>
+      </c>
+      <c r="F111" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="33" t="n">
+        <v>8.35</v>
       </c>
       <c r="H111" s="33">
-        <f>SUM(H102:H110)</f>
+        <f>F111*G111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>Estes 18in Rip-Stop Nylon Parachute</t>
+        </is>
+      </c>
+      <c r="B112" s="33" t="inlineStr">
+        <is>
+          <t>Estes</t>
+        </is>
+      </c>
+      <c r="C112" s="33" t="inlineStr">
+        <is>
+          <t>18in chute</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E112" s="33" t="inlineStr">
+        <is>
+          <t>in cart; design/sims use 24in canopy only (Mathematics.md sec6) - confirm intended use (spare/drogue) or remove</t>
+        </is>
+      </c>
+      <c r="F112" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="H112" s="33">
+        <f>F112*G112</f>
         <v/>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="34">
       <c r="A113" s="33" t="inlineStr">
         <is>
-          <t>10. Field/Support Equipment (magnets, ground-test smoke)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="34">
-      <c r="A114" s="33" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B114" s="33" t="inlineStr">
-        <is>
-          <t>Storefront</t>
-        </is>
-      </c>
-      <c r="C114" s="33" t="inlineStr">
-        <is>
-          <t>Part # / Spec</t>
-        </is>
-      </c>
-      <c r="D114" s="33" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="E114" s="33" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="F114" s="33" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="G114" s="33" t="inlineStr">
-        <is>
-          <t>Unit ($)</t>
-        </is>
-      </c>
-      <c r="H114" s="33" t="inlineStr">
-        <is>
-          <t>Line ($)</t>
-        </is>
-      </c>
-    </row>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="H113" s="33">
+        <f>SUM(H104:H112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="34"/>
     <row r="115" ht="15" customHeight="1" s="34">
       <c r="A115" s="33" t="inlineStr">
         <is>
-          <t>TRYMAG small neodymium magnets, 6x2mm, 100-pack</t>
-        </is>
-      </c>
-      <c r="B115" s="33" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="C115" s="33" t="inlineStr">
-        <is>
-          <t>B0D9BJV84F</t>
-        </is>
-      </c>
-      <c r="D115" s="33" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="E115" s="33" t="inlineStr">
-        <is>
-          <t>NOT IN CURRENT CART (2026-08-09e) - live cart has Caturledas 6x2mm-250pack instead (row 123), zeroed to avoid double-buying the same size.</t>
-        </is>
-      </c>
-      <c r="F115" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="33">
-        <f>F115*G115</f>
-        <v/>
+          <t>10. Field/Support Equipment (magnets, ground-test smoke)</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="34">
       <c r="A116" s="33" t="inlineStr">
         <is>
-          <t>VSKIZ small neodymium magnets, 10x3mm, 50-pack</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B116" s="33" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Storefront</t>
         </is>
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>B0BVY5VYQY</t>
+          <t>Part # / Spec</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="E116" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09: added per request. Same VSKIZ listing also offers a 6x2mm-120p size variant if consolidating to one seller is preferred.</t>
-        </is>
-      </c>
-      <c r="F116" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="33" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="H116" s="33">
-        <f>F116*G116</f>
-        <v/>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F116" s="33" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="G116" s="33" t="inlineStr">
+        <is>
+          <t>Unit ($)</t>
+        </is>
+      </c>
+      <c r="H116" s="33" t="inlineStr">
+        <is>
+          <t>Line ($)</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="34">
       <c r="A117" s="33" t="inlineStr">
         <is>
-          <t>COLBOR CF3 30W portable rechargeable fog machine (photography/ground-test smoke)</t>
+          <t>TRYMAG small neodymium magnets, 6x2mm, 100-pack</t>
         </is>
       </c>
       <c r="B117" s="33" t="inlineStr">
@@ -4067,7 +4080,7 @@
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
-          <t>B0FW4VQ72H</t>
+          <t>B0D9BJV84F</t>
         </is>
       </c>
       <c r="D117" s="33" t="inlineStr">
@@ -4077,14 +4090,14 @@
       </c>
       <c r="E117" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09: added per request, CF3 (smaller) size selected over CF5.</t>
+          <t>NOT IN CURRENT CART (2026-08-09e) - live cart has Caturledas 6x2mm-250pack instead (row 123), zeroed to avoid double-buying the same size.</t>
         </is>
       </c>
       <c r="F117" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="33" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H117" s="33">
         <f>F117*G117</f>
@@ -4094,7 +4107,7 @@
     <row r="118" ht="15" customHeight="1" s="34">
       <c r="A118" s="33" t="inlineStr">
         <is>
-          <t>OXLasers 520nm focusable green line laser module (positioning/alignment)</t>
+          <t>VSKIZ small neodymium magnets, 10x3mm, 50-pack</t>
         </is>
       </c>
       <c r="B118" s="33" t="inlineStr">
@@ -4104,7 +4117,7 @@
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>B0CKP4SYL7</t>
+          <t>B0BVY5VYQY</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
@@ -4114,14 +4127,14 @@
       </c>
       <c r="E118" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09e: in live Amazon cart.</t>
+          <t>2026-08-13: in cart at $8.99 (limited-time deal, was $9.99).</t>
         </is>
       </c>
       <c r="F118" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="33" t="n">
-        <v>39</v>
+        <v>8.99</v>
       </c>
       <c r="H118" s="33">
         <f>F118*G118</f>
@@ -4131,7 +4144,7 @@
     <row r="119" ht="15" customHeight="1" s="34">
       <c r="A119" s="33" t="inlineStr">
         <is>
-          <t>Loc-Line 1/4in modular hose sample kit (flexible positioning/coolant hose)</t>
+          <t>COLBOR CF3 30W portable rechargeable fog machine (photography/ground-test smoke)</t>
         </is>
       </c>
       <c r="B119" s="33" t="inlineStr">
@@ -4141,7 +4154,7 @@
       </c>
       <c r="C119" s="33" t="inlineStr">
         <is>
-          <t>B0GZL8N636</t>
+          <t>B0FW4VQ72H</t>
         </is>
       </c>
       <c r="D119" s="33" t="inlineStr">
@@ -4151,14 +4164,14 @@
       </c>
       <c r="E119" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09e: in live Amazon cart.</t>
+          <t>2026-08-13: in cart at $89.00 (was listed $75). CF3 size selected over CF5.</t>
         </is>
       </c>
       <c r="F119" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="33" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="H119" s="33">
         <f>F119*G119</f>
@@ -4168,7 +4181,7 @@
     <row r="120" ht="15" customHeight="1" s="34">
       <c r="A120" s="33" t="inlineStr">
         <is>
-          <t>SmallRig P96L RGB portable video light (photo/video documentation)</t>
+          <t>OXLasers 520nm focusable green line laser module (positioning/alignment)</t>
         </is>
       </c>
       <c r="B120" s="33" t="inlineStr">
@@ -4178,7 +4191,7 @@
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>B09G98NRQZ</t>
+          <t>B0CKP4SYL7</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
@@ -4188,14 +4201,14 @@
       </c>
       <c r="E120" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09e: in live Amazon cart.</t>
+          <t>2026-08-13: in cart at $39.00. Alignment/positioning line laser for the stands and the bend rig.</t>
         </is>
       </c>
       <c r="F120" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="33" t="n">
-        <v>35.99</v>
+        <v>39</v>
       </c>
       <c r="H120" s="33">
         <f>F120*G120</f>
@@ -4205,7 +4218,7 @@
     <row r="121" ht="15" customHeight="1" s="34">
       <c r="A121" s="33" t="inlineStr">
         <is>
-          <t>80 Mesh 304 stainless steel woven wire mesh, 5-pack, 7.8x11.8in</t>
+          <t>Loc-Line 1/4in modular hose sample kit (flexible positioning/coolant hose)</t>
         </is>
       </c>
       <c r="B121" s="33" t="inlineStr">
@@ -4215,7 +4228,7 @@
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>B09VNKDS9R</t>
+          <t>B0GZL8N636</t>
         </is>
       </c>
       <c r="D121" s="33" t="inlineStr">
@@ -4225,14 +4238,14 @@
       </c>
       <c r="E121" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09e: in live Amazon cart.</t>
+          <t>2026-08-13: in cart at $25.00. Ships Aug 17-18, earliest item in the cart.</t>
         </is>
       </c>
       <c r="F121" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="33" t="n">
-        <v>7.99</v>
+        <v>25</v>
       </c>
       <c r="H121" s="33">
         <f>F121*G121</f>
@@ -4242,7 +4255,7 @@
     <row r="122" ht="15" customHeight="1" s="34">
       <c r="A122" s="33" t="inlineStr">
         <is>
-          <t>40 Mesh 304 stainless steel wire mesh, ANGELIOX, 2-pack, 12x45in</t>
+          <t>SmallRig P96L RGB portable video light (photo/video documentation)</t>
         </is>
       </c>
       <c r="B122" s="33" t="inlineStr">
@@ -4252,7 +4265,7 @@
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>B0BBMTDK88</t>
+          <t>B09G98NRQZ</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
@@ -4262,14 +4275,14 @@
       </c>
       <c r="E122" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09e: in live Amazon cart.</t>
+          <t>2026-08-13: in cart at $30.60 (was $35.99).</t>
         </is>
       </c>
       <c r="F122" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="33" t="n">
-        <v>15.99</v>
+        <v>30.6</v>
       </c>
       <c r="H122" s="33">
         <f>F122*G122</f>
@@ -4279,7 +4292,7 @@
     <row r="123" ht="15" customHeight="1" s="34">
       <c r="A123" s="33" t="inlineStr">
         <is>
-          <t>Caturledas small neodymium magnets, 6x2mm, 250-pack</t>
+          <t>80 Mesh 304 stainless steel woven wire mesh, 5-pack, 7.8x11.8in</t>
         </is>
       </c>
       <c r="B123" s="33" t="inlineStr">
@@ -4289,7 +4302,7 @@
       </c>
       <c r="C123" s="33" t="inlineStr">
         <is>
-          <t>B0DBVJF1G2</t>
+          <t>B09VNKDS9R</t>
         </is>
       </c>
       <c r="D123" s="33" t="inlineStr">
@@ -4299,14 +4312,14 @@
       </c>
       <c r="E123" s="33" t="inlineStr">
         <is>
-          <t>2026-08-09e: actual cart item for 6x2mm size (Caturledas 250-pack, not TRYMAG 100-pack row 115 - superseded).</t>
+          <t>2026-08-13: in cart at $7.99. Only 15 left in stock.</t>
         </is>
       </c>
       <c r="F123" s="33" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="33" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="H123" s="33">
         <f>F123*G123</f>
@@ -4316,11 +4329,85 @@
     <row r="124" ht="15" customHeight="1" s="34">
       <c r="A124" s="33" t="inlineStr">
         <is>
+          <t>40 Mesh 304 stainless steel wire mesh, ANGELIOX, 2-pack, 12x45in</t>
+        </is>
+      </c>
+      <c r="B124" s="33" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C124" s="33" t="inlineStr">
+        <is>
+          <t>B0BBMTDK88</t>
+        </is>
+      </c>
+      <c r="D124" s="33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E124" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-13: in cart at $15.99. Only 10 left in stock.</t>
+        </is>
+      </c>
+      <c r="F124" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="33" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="H124" s="33">
+        <f>F124*G124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="33" t="inlineStr">
+        <is>
+          <t>Caturledas small neodymium magnets, 6x2mm, 250-pack</t>
+        </is>
+      </c>
+      <c r="B125" s="33" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C125" s="33" t="inlineStr">
+        <is>
+          <t>B0DBVJF1G2</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E125" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-13: in cart at $9.99.</t>
+        </is>
+      </c>
+      <c r="F125" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="33" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H125" s="33">
+        <f>F125*G125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="33" t="inlineStr">
+        <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="H124" s="33">
-        <f>SUM(H115:H123)</f>
+      <c r="H126" s="33">
+        <f>SUM(H117:H125)</f>
         <v/>
       </c>
     </row>
@@ -4387,7 +4474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="50" customWidth="1" style="33" min="1" max="1"/>
@@ -5268,19 +5355,389 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="34">
-      <c r="A27" s="59" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>microSD SPI breakout board (flight FC data of record)</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>PID 254</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>owned - confirmed on hand 2026-08-13; SPI1 on the Pico 2 W</t>
+        </is>
+      </c>
+      <c r="F27" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="H27" s="46">
+        <f>F27*G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Bulk cap 470 uF 10 V low-ESR + 100 nF ceramic</t>
+        </is>
+      </c>
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C28" s="42" t="inlineStr">
+        <is>
+          <t>470uF + 100nF</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>on hand - servo-feed bulk + ADC tap decoupling</t>
+        </is>
+      </c>
+      <c r="F28" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" s="46">
+        <f>F28*G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>100 kohm / 47 kohm 1% metal-film resistors (battery divider)</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>1% metal-film</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E29" s="44" t="inlineStr">
+        <is>
+          <t>on hand - VERIFY values match WYV_VBAT_DIV_TOP/BOT before soldering</t>
+        </is>
+      </c>
+      <c r="F29" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="46">
+        <f>F29*G29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>24 AWG flexible silicone wire, 6-color</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>24 AWG silicone</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>on hand</t>
+        </is>
+      </c>
+      <c r="F30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="46" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" s="46">
+        <f>F30*G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Multi-colored heat-shrink assortment</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>heat-shrink pack</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="inlineStr">
+        <is>
+          <t>on hand</t>
+        </is>
+      </c>
+      <c r="F31" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="46">
+        <f>F31*G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>High-temp polyimide (Kapton) tape</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>Kapton 1 cm</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>on hand</t>
+        </is>
+      </c>
+      <c r="F32" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" s="46">
+        <f>F32*G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Male header, 36-pin breakaway</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>2.54 mm header</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="inlineStr">
+        <is>
+          <t>on hand</t>
+        </is>
+      </c>
+      <c r="F33" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="46">
+        <f>F33*G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>Nomex chute protector blanket</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>12x12 in Nomex</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>on hand - ejection-gas shield</t>
+        </is>
+      </c>
+      <c r="F34" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" s="46">
+        <f>F34*G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>1010 launch rail + pad</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>Estes/Amazon</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>1010 rail</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="inlineStr">
+        <is>
+          <t>on hand - rail-exit gate is 1.0 m</t>
+        </is>
+      </c>
+      <c r="F35" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="46" t="n">
+        <v>45</v>
+      </c>
+      <c r="H35" s="46">
+        <f>F35*G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Estes F15-4 flight motors (2 on hand)</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>Estes</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>F15-4</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>on hand 2026-08-14; 2 more on order = 4 total flight motors</t>
+        </is>
+      </c>
+      <c r="F36" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="46" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" s="46">
+        <f>F36*G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="inlineStr">
         <is>
           <t>Total already paid</t>
         </is>
       </c>
-      <c r="B27" s="60" t="n"/>
-      <c r="C27" s="60" t="n"/>
-      <c r="D27" s="60" t="n"/>
-      <c r="E27" s="60" t="n"/>
-      <c r="F27" s="60" t="n"/>
-      <c r="G27" s="60" t="n"/>
-      <c r="H27" s="61">
-        <f>SUM(H4:H26)</f>
+      <c r="B37" s="60" t="n"/>
+      <c r="C37" s="60" t="n"/>
+      <c r="D37" s="60" t="n"/>
+      <c r="E37" s="60" t="n"/>
+      <c r="F37" s="60" t="n"/>
+      <c r="G37" s="60" t="n"/>
+      <c r="H37" s="61">
+        <f>SUM(H4:H36)</f>
         <v/>
       </c>
     </row>
@@ -5394,11 +5851,11 @@
     <row r="8" ht="15" customHeight="1" s="34">
       <c r="A8" s="53" t="inlineStr">
         <is>
-          <t>6. Airframe filament (Amazon + Bambu Lab - see flag notes, scope mismatch vs PLA/PETG-CF design)</t>
+          <t>6. Airframe filament (flown zoning + RQ2 comparison stock)</t>
         </is>
       </c>
       <c r="B8" s="62">
-        <f>BOM!H56</f>
+        <f>BOM!H58</f>
         <v/>
       </c>
     </row>
@@ -5409,7 +5866,7 @@
         </is>
       </c>
       <c r="B9" s="62">
-        <f>BOM!H84</f>
+        <f>BOM!H86</f>
         <v/>
       </c>
     </row>
@@ -5420,18 +5877,18 @@
         </is>
       </c>
       <c r="B10" s="62">
-        <f>BOM!H94</f>
+        <f>BOM!H96</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="34">
       <c r="A11" s="33" t="inlineStr">
         <is>
-          <t>9. 2026-08-09 Cart Reconciliation &amp; Custom PCB</t>
+          <t>9. Cart reconciliation, load cells, retired PCB</t>
         </is>
       </c>
       <c r="B11" s="33">
-        <f>BOM!H111</f>
+        <f>BOM!H113</f>
         <v/>
       </c>
     </row>
@@ -5442,7 +5899,7 @@
         </is>
       </c>
       <c r="B12" s="33">
-        <f>BOM!H124</f>
+        <f>BOM!H126</f>
         <v/>
       </c>
     </row>
@@ -5453,7 +5910,7 @@
         </is>
       </c>
       <c r="B13" s="64">
-        <f>BOM!H96</f>
+        <f>BOM!H98</f>
         <v/>
       </c>
     </row>
@@ -5475,7 +5932,7 @@
         </is>
       </c>
       <c r="B15" s="66">
-        <f>BOM!H98</f>
+        <f>BOM!H100</f>
         <v/>
       </c>
     </row>
@@ -5487,7 +5944,7 @@
         </is>
       </c>
       <c r="B17" s="64">
-        <f>'Already Acquired'!H27</f>
+        <f>'Already Acquired'!H37</f>
         <v/>
       </c>
     </row>
